--- a/resources/templates/summary.xlsx
+++ b/resources/templates/summary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC-4\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC-4\Box\【基本】Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC7BAF8-8BD5-41DD-B19B-6BE803DD4CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B758E298-0A26-474F-A8B9-911D49442821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3FED3C94-5D07-4FC9-9927-EED4C83E9AF2}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <definedName name="_msoanchor_1" localSheetId="0">表紙!$I$7</definedName>
     <definedName name="_msoanchor_2" localSheetId="0">表紙!#REF!</definedName>
     <definedName name="_msocom_1" localSheetId="0">表紙!$A$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">内訳書!$A$1:$K$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">内訳書!$A$1:$K$75</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$K$36</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="89">
   <si>
     <t>御 見 積 書</t>
   </si>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>単位</t>
-  </si>
-  <si>
-    <t>単　価</t>
   </si>
   <si>
     <t>金額</t>
@@ -610,19 +607,32 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>合計</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウケイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>単価</t>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="9">
     <numFmt numFmtId="6" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
     <numFmt numFmtId="176" formatCode="&quot;¥&quot;#,##0_);[Red]\(&quot;¥&quot;#,##0\)"/>
     <numFmt numFmtId="177" formatCode="#,##0_ "/>
     <numFmt numFmtId="178" formatCode="&quot;¥&quot;#,##0.00_);[Red]\(&quot;¥&quot;#,##0.00\)"/>
     <numFmt numFmtId="179" formatCode="#,##0.0_ "/>
     <numFmt numFmtId="180" formatCode="&quot;¥&quot;#,##0_);\(&quot;¥&quot;#,##0\)"/>
-    <numFmt numFmtId="188" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
+    <numFmt numFmtId="181" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
+    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\)"/>
+    <numFmt numFmtId="183" formatCode="0.0_);\(0.0\)"/>
   </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
@@ -753,7 +763,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -996,21 +1006,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1378,6 +1373,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1391,7 +1425,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1440,24 +1474,8 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -1468,13 +1486,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1499,9 +1510,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -1520,41 +1528,14 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1564,30 +1545,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1621,6 +1578,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="2" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="2" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
@@ -1631,81 +1591,17 @@
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="2" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="37" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="180" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1723,18 +1619,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1771,124 +1655,270 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1899,7 +1929,7 @@
   </cellStyles>
   <dxfs count="1">
     <dxf>
-      <numFmt numFmtId="183" formatCode="&quot;令和元年&quot;m&quot;月&quot;d&quot;日&quot;"/>
+      <numFmt numFmtId="184" formatCode="&quot;令和元年&quot;m&quot;月&quot;d&quot;日&quot;"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2047,7 +2077,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
+      <xdr:colOff>238125</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
@@ -2291,7 +2321,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
@@ -2352,7 +2382,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>19050</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
@@ -2413,7 +2443,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
@@ -3599,13 +3629,13 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="4.125" customWidth="1"/>
-    <col min="2" max="2" width="23.75" style="4" customWidth="1"/>
-    <col min="3" max="3" width="8.375" customWidth="1"/>
+    <col min="2" max="2" width="23.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="7.625" customWidth="1"/>
     <col min="4" max="4" width="10.625" customWidth="1"/>
-    <col min="5" max="5" width="24.25" customWidth="1"/>
-    <col min="6" max="6" width="9.875" customWidth="1"/>
-    <col min="7" max="7" width="6.375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="5" max="5" width="24.625" customWidth="1"/>
+    <col min="6" max="6" width="9.625" customWidth="1"/>
+    <col min="7" max="7" width="6.625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="12.625" customWidth="1"/>
     <col min="9" max="10" width="10.625" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
@@ -3875,19 +3905,19 @@
       <c r="IE5" s="1"/>
     </row>
     <row r="6" spans="1:239" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="19"/>
+      <c r="B6" s="115"/>
+      <c r="C6" s="115"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="116"/>
       <c r="L6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -4117,22 +4147,22 @@
       <c r="IE6" s="2"/>
     </row>
     <row r="7" spans="1:239" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="20"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="153">
+      <c r="A7" s="17"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="120"/>
+      <c r="D7" s="122" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="117">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
-      </c>
-      <c r="J7" s="153"/>
-      <c r="K7" s="25"/>
+        <v>46312</v>
+      </c>
+      <c r="J7" s="117"/>
+      <c r="K7" s="20"/>
       <c r="L7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -4362,17 +4392,17 @@
       <c r="IE7" s="1"/>
     </row>
     <row r="8" spans="1:239" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="20"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="25"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="20"/>
       <c r="L8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -4602,17 +4632,17 @@
       <c r="IE8" s="1"/>
     </row>
     <row r="9" spans="1:239" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="25"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="20"/>
       <c r="L9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -4842,21 +4872,21 @@
       <c r="IE9" s="1"/>
     </row>
     <row r="10" spans="1:239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="30" t="s">
+      <c r="A10" s="17"/>
+      <c r="B10" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32" t="s">
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="I10" s="24"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="33"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="26"/>
       <c r="L10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -5086,17 +5116,17 @@
       <c r="IE10" s="1"/>
     </row>
     <row r="11" spans="1:239" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="33"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="26"/>
       <c r="L11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -5326,24 +5356,24 @@
       <c r="IE11" s="1"/>
     </row>
     <row r="12" spans="1:239" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="34" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="140">
         <f>I33</f>
         <v>0</v>
       </c>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="I12" s="24"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="33"/>
+      <c r="D12" s="140"/>
+      <c r="E12" s="140"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12" s="19"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="26"/>
       <c r="L12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -5573,19 +5603,19 @@
       <c r="IE12" s="1"/>
     </row>
     <row r="13" spans="1:239" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="24"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="33"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="19"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="26"/>
       <c r="L13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -5815,19 +5845,19 @@
       <c r="IE13" s="1"/>
     </row>
     <row r="14" spans="1:239" ht="17.25" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="39"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="33"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="31"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="26"/>
       <c r="L14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -6057,21 +6087,21 @@
       <c r="IE14" s="1"/>
     </row>
     <row r="15" spans="1:239" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="I15" s="32"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="33"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="132" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="124"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="126"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" s="25"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="26"/>
       <c r="L15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -6301,19 +6331,19 @@
       <c r="IE15" s="1"/>
     </row>
     <row r="16" spans="1:239" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
-      <c r="B16" s="48"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="I16" s="52"/>
-      <c r="J16" s="53"/>
-      <c r="K16" s="33"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="133"/>
+      <c r="C16" s="127"/>
+      <c r="D16" s="128"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16" s="37"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="26"/>
       <c r="L16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -6543,21 +6573,21 @@
       <c r="IE16" s="1"/>
     </row>
     <row r="17" spans="1:239" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="54" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="55"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="52" t="s">
-        <v>81</v>
-      </c>
-      <c r="I17" s="52"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="33"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="134"/>
+      <c r="D17" s="135"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" s="37"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="26"/>
       <c r="L17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -6787,21 +6817,21 @@
       <c r="IE17" s="1"/>
     </row>
     <row r="18" spans="1:239" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="54" t="s">
+      <c r="A18" s="17"/>
+      <c r="B18" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="58" t="s">
-        <v>78</v>
-      </c>
-      <c r="D18" s="59"/>
-      <c r="E18" s="60"/>
+      <c r="C18" s="137" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="138"/>
+      <c r="E18" s="139"/>
       <c r="F18" s="4"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="32"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="25"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="62"/>
+      <c r="K18" s="41"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -7029,21 +7059,21 @@
       <c r="IB18" s="1"/>
     </row>
     <row r="19" spans="1:239" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="63" t="s">
+      <c r="A19" s="17"/>
+      <c r="B19" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="64" t="s">
+      <c r="C19" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="65"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="67"/>
-      <c r="G19" s="68"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="30"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="23"/>
       <c r="J19" s="4"/>
-      <c r="K19" s="33"/>
+      <c r="K19" s="26"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -7271,17 +7301,17 @@
       <c r="IB19" s="1"/>
     </row>
     <row r="20" spans="1:239" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="24"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="19"/>
       <c r="J20" s="4"/>
-      <c r="K20" s="70"/>
+      <c r="K20" s="49"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -7512,28 +7542,30 @@
       <c r="IE20" s="1"/>
     </row>
     <row r="21" spans="1:239" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="71"/>
-      <c r="B21" s="72" t="s">
+      <c r="A21" s="50"/>
+      <c r="B21" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="73"/>
-      <c r="D21" s="71" t="s">
+      <c r="C21" s="52"/>
+      <c r="D21" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="74"/>
-      <c r="F21" s="75"/>
-      <c r="G21" s="76" t="s">
+      <c r="E21" s="53"/>
+      <c r="F21" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="G21" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="76" t="s">
+      <c r="H21" s="55" t="s">
+        <v>88</v>
+      </c>
+      <c r="I21" s="118" t="s">
         <v>10</v>
       </c>
-      <c r="I21" s="77" t="s">
+      <c r="J21" s="119"/>
+      <c r="K21" s="55" t="s">
         <v>11</v>
-      </c>
-      <c r="J21" s="78"/>
-      <c r="K21" s="76" t="s">
-        <v>12</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -7764,20 +7796,20 @@
       <c r="ID21" s="1"/>
     </row>
     <row r="22" spans="1:239" ht="20.25" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="79"/>
-      <c r="B22" s="80"/>
-      <c r="C22" s="81"/>
-      <c r="D22" s="82"/>
-      <c r="E22" s="83"/>
-      <c r="F22" s="84"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="86"/>
-      <c r="I22" s="87">
+      <c r="A22" s="56"/>
+      <c r="B22" s="86"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="91"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="107"/>
+      <c r="I22" s="130">
         <f>F22*H22</f>
         <v>0</v>
       </c>
-      <c r="J22" s="88"/>
-      <c r="K22" s="89"/>
+      <c r="J22" s="131"/>
+      <c r="K22" s="57"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
@@ -8008,20 +8040,20 @@
       <c r="IE22" s="3"/>
     </row>
     <row r="23" spans="1:239" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="79"/>
-      <c r="B23" s="90"/>
-      <c r="C23" s="81"/>
-      <c r="D23" s="82"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="84"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="91">
+      <c r="A23" s="56"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="106"/>
+      <c r="H23" s="107"/>
+      <c r="I23" s="108">
         <f t="shared" ref="I23:I32" si="0">F23*H23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="92"/>
-      <c r="K23" s="89"/>
+      <c r="J23" s="109"/>
+      <c r="K23" s="57"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
@@ -8252,20 +8284,20 @@
       <c r="IE23" s="3"/>
     </row>
     <row r="24" spans="1:239" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="79"/>
-      <c r="B24" s="93"/>
-      <c r="C24" s="81"/>
-      <c r="D24" s="82"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="84"/>
-      <c r="G24" s="85"/>
-      <c r="H24" s="86"/>
-      <c r="I24" s="91">
+      <c r="A24" s="56"/>
+      <c r="B24" s="88"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="90"/>
+      <c r="E24" s="91"/>
+      <c r="F24" s="92"/>
+      <c r="G24" s="106"/>
+      <c r="H24" s="107"/>
+      <c r="I24" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J24" s="92"/>
-      <c r="K24" s="89"/>
+      <c r="J24" s="109"/>
+      <c r="K24" s="57"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
@@ -8496,20 +8528,20 @@
       <c r="IE24" s="3"/>
     </row>
     <row r="25" spans="1:239" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="79"/>
-      <c r="B25" s="93"/>
-      <c r="C25" s="81"/>
-      <c r="D25" s="82"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="94"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="91">
+      <c r="A25" s="56"/>
+      <c r="B25" s="88"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="90"/>
+      <c r="E25" s="91"/>
+      <c r="F25" s="92"/>
+      <c r="G25" s="106"/>
+      <c r="H25" s="107"/>
+      <c r="I25" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J25" s="92"/>
-      <c r="K25" s="89"/>
+      <c r="J25" s="109"/>
+      <c r="K25" s="57"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -8740,20 +8772,20 @@
       <c r="IE25" s="3"/>
     </row>
     <row r="26" spans="1:239" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="79"/>
-      <c r="B26" s="93"/>
-      <c r="C26" s="81"/>
-      <c r="D26" s="82"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="84"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="91">
+      <c r="A26" s="56"/>
+      <c r="B26" s="88"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="90"/>
+      <c r="E26" s="91"/>
+      <c r="F26" s="92"/>
+      <c r="G26" s="106"/>
+      <c r="H26" s="107"/>
+      <c r="I26" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J26" s="92"/>
-      <c r="K26" s="89"/>
+      <c r="J26" s="109"/>
+      <c r="K26" s="57"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
@@ -8984,20 +9016,20 @@
       <c r="IE26" s="3"/>
     </row>
     <row r="27" spans="1:239" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="79"/>
-      <c r="B27" s="93"/>
-      <c r="C27" s="81"/>
-      <c r="D27" s="82"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="84"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="86"/>
-      <c r="I27" s="91">
+      <c r="A27" s="56"/>
+      <c r="B27" s="88"/>
+      <c r="C27" s="89"/>
+      <c r="D27" s="90"/>
+      <c r="E27" s="91"/>
+      <c r="F27" s="92"/>
+      <c r="G27" s="106"/>
+      <c r="H27" s="107"/>
+      <c r="I27" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="92"/>
-      <c r="K27" s="89"/>
+      <c r="J27" s="109"/>
+      <c r="K27" s="57"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
@@ -9228,20 +9260,20 @@
       <c r="IE27" s="3"/>
     </row>
     <row r="28" spans="1:239" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="79"/>
-      <c r="B28" s="93"/>
-      <c r="C28" s="81"/>
-      <c r="D28" s="82"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="84"/>
-      <c r="G28" s="85"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="91">
+      <c r="A28" s="56"/>
+      <c r="B28" s="88"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="90"/>
+      <c r="E28" s="91"/>
+      <c r="F28" s="92"/>
+      <c r="G28" s="106"/>
+      <c r="H28" s="107"/>
+      <c r="I28" s="108">
         <f>F28*H28</f>
         <v>0</v>
       </c>
-      <c r="J28" s="92"/>
-      <c r="K28" s="89"/>
+      <c r="J28" s="109"/>
+      <c r="K28" s="57"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -9472,20 +9504,20 @@
       <c r="IE28" s="3"/>
     </row>
     <row r="29" spans="1:239" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="79"/>
-      <c r="B29" s="93"/>
-      <c r="C29" s="81"/>
-      <c r="D29" s="82"/>
-      <c r="E29" s="83"/>
-      <c r="F29" s="84"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="86"/>
-      <c r="I29" s="91">
+      <c r="A29" s="56"/>
+      <c r="B29" s="88"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="91"/>
+      <c r="F29" s="92"/>
+      <c r="G29" s="106"/>
+      <c r="H29" s="107"/>
+      <c r="I29" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J29" s="92"/>
-      <c r="K29" s="89"/>
+      <c r="J29" s="109"/>
+      <c r="K29" s="57"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
@@ -9716,20 +9748,20 @@
       <c r="IE29" s="3"/>
     </row>
     <row r="30" spans="1:239" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="79"/>
-      <c r="B30" s="93"/>
-      <c r="C30" s="81"/>
-      <c r="D30" s="82"/>
-      <c r="E30" s="83"/>
-      <c r="F30" s="84"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="86"/>
-      <c r="I30" s="91">
+      <c r="A30" s="56"/>
+      <c r="B30" s="88"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="90"/>
+      <c r="E30" s="91"/>
+      <c r="F30" s="92"/>
+      <c r="G30" s="106"/>
+      <c r="H30" s="107"/>
+      <c r="I30" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J30" s="92"/>
-      <c r="K30" s="89"/>
+      <c r="J30" s="109"/>
+      <c r="K30" s="57"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
@@ -9960,22 +9992,22 @@
       <c r="IE30" s="3"/>
     </row>
     <row r="31" spans="1:239" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="79"/>
-      <c r="B31" s="93"/>
-      <c r="C31" s="81"/>
-      <c r="D31" s="82" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="83"/>
-      <c r="F31" s="84"/>
-      <c r="G31" s="85"/>
-      <c r="H31" s="86"/>
-      <c r="I31" s="91">
+      <c r="A31" s="56"/>
+      <c r="B31" s="88"/>
+      <c r="C31" s="89"/>
+      <c r="D31" s="90" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="91"/>
+      <c r="F31" s="92"/>
+      <c r="G31" s="106"/>
+      <c r="H31" s="107"/>
+      <c r="I31" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J31" s="92"/>
-      <c r="K31" s="89"/>
+      <c r="J31" s="109"/>
+      <c r="K31" s="57"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
@@ -10206,20 +10238,20 @@
       <c r="IE31" s="3"/>
     </row>
     <row r="32" spans="1:239" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="79"/>
-      <c r="B32" s="93"/>
-      <c r="C32" s="81"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="84"/>
-      <c r="G32" s="85"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="91">
+      <c r="A32" s="56"/>
+      <c r="B32" s="88"/>
+      <c r="C32" s="89"/>
+      <c r="D32" s="90"/>
+      <c r="E32" s="91"/>
+      <c r="F32" s="92"/>
+      <c r="G32" s="106"/>
+      <c r="H32" s="107"/>
+      <c r="I32" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J32" s="92"/>
-      <c r="K32" s="95"/>
+      <c r="J32" s="109"/>
+      <c r="K32" s="58"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
@@ -10450,22 +10482,24 @@
       <c r="IE32" s="3"/>
     </row>
     <row r="33" spans="1:239" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="96" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" s="97"/>
-      <c r="C33" s="98"/>
-      <c r="D33" s="98"/>
-      <c r="E33" s="99"/>
-      <c r="F33" s="100"/>
-      <c r="G33" s="100"/>
-      <c r="H33" s="101"/>
-      <c r="I33" s="102">
+      <c r="A33" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="60"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="110" t="s">
+        <v>87</v>
+      </c>
+      <c r="G33" s="110"/>
+      <c r="H33" s="111"/>
+      <c r="I33" s="112">
         <f>SUM(I22:J32)</f>
         <v>0</v>
       </c>
-      <c r="J33" s="103"/>
-      <c r="K33" s="104"/>
+      <c r="J33" s="113"/>
+      <c r="K33" s="63"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
@@ -10696,17 +10730,17 @@
       <c r="IE33" s="1"/>
     </row>
     <row r="34" spans="1:239" x14ac:dyDescent="0.2">
-      <c r="A34" s="105"/>
-      <c r="B34" s="98"/>
-      <c r="C34" s="98"/>
-      <c r="D34" s="98"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="98"/>
-      <c r="G34" s="106"/>
+      <c r="A34" s="64"/>
+      <c r="B34" s="61"/>
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="65"/>
       <c r="H34" s="4"/>
       <c r="I34" s="11"/>
       <c r="J34" s="4"/>
-      <c r="K34" s="107"/>
+      <c r="K34" s="66"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
@@ -10937,19 +10971,19 @@
       <c r="IE34" s="1"/>
     </row>
     <row r="35" spans="1:239" x14ac:dyDescent="0.2">
-      <c r="A35" s="108"/>
-      <c r="B35" s="109"/>
-      <c r="C35" s="109"/>
-      <c r="D35" s="109"/>
-      <c r="E35" s="109"/>
-      <c r="F35" s="109"/>
-      <c r="G35" s="110"/>
-      <c r="H35" s="111" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" s="111"/>
-      <c r="J35" s="111"/>
-      <c r="K35" s="112"/>
+      <c r="A35" s="67"/>
+      <c r="B35" s="68"/>
+      <c r="C35" s="68"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="70" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="70"/>
+      <c r="J35" s="70"/>
+      <c r="K35" s="71"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
@@ -11180,7 +11214,7 @@
       <c r="IE35" s="1"/>
     </row>
     <row r="36" spans="1:239" x14ac:dyDescent="0.15">
-      <c r="A36" s="113"/>
+      <c r="A36" s="72"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -13372,2528 +13406,2528 @@
     <col min="4" max="4" width="10.625" customWidth="1"/>
     <col min="5" max="5" width="24.625" customWidth="1"/>
     <col min="6" max="6" width="9.625" customWidth="1"/>
-    <col min="7" max="7" width="5.625" customWidth="1"/>
-    <col min="8" max="8" width="10.625" customWidth="1"/>
+    <col min="7" max="7" width="7.625" customWidth="1"/>
+    <col min="8" max="8" width="12.625" customWidth="1"/>
     <col min="9" max="10" width="11.625" customWidth="1"/>
-    <col min="11" max="11" width="16.625" customWidth="1"/>
+    <col min="11" max="11" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="114" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="115">
+      <c r="A1" s="141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="141"/>
+      <c r="C1" s="142">
         <f>表紙!C15</f>
         <v>0</v>
       </c>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="116" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="114" t="s">
-        <v>76</v>
-      </c>
-      <c r="K1" s="114"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="143" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="144" t="s">
+        <v>75</v>
+      </c>
+      <c r="K1" s="144"/>
     </row>
     <row r="2" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="117"/>
-      <c r="B2" s="118" t="s">
+      <c r="A2" s="73"/>
+      <c r="B2" s="152" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="120" t="s">
+      <c r="C2" s="151"/>
+      <c r="D2" s="150" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="121"/>
-      <c r="F2" s="122" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="122" t="s">
+      <c r="E2" s="151"/>
+      <c r="F2" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="122" t="s">
+      <c r="H2" s="78" t="s">
+        <v>88</v>
+      </c>
+      <c r="I2" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="123" t="s">
+      <c r="J2" s="146"/>
+      <c r="K2" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="124"/>
-      <c r="K2" s="122" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="3" spans="1:11" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="125"/>
-      <c r="B3" s="126"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="128"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="131"/>
-      <c r="H3" s="132"/>
-      <c r="I3" s="133">
+      <c r="A3" s="100"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="149">
         <f>SUM(F3*H3)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="134"/>
-      <c r="K3" s="135"/>
+      <c r="J3" s="148"/>
+      <c r="K3" s="80"/>
     </row>
     <row r="4" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="136"/>
-      <c r="B4" s="137"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="139"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="131"/>
-      <c r="H4" s="132"/>
-      <c r="I4" s="133">
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="149">
         <f>SUM(F4*H4)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="134"/>
-      <c r="K4" s="135"/>
+      <c r="J4" s="148"/>
+      <c r="K4" s="80"/>
     </row>
     <row r="5" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="136"/>
-      <c r="B5" s="140"/>
-      <c r="C5" s="138"/>
-      <c r="D5" s="139"/>
-      <c r="E5" s="129"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="131"/>
-      <c r="H5" s="132"/>
-      <c r="I5" s="133">
+      <c r="A5" s="81"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="102"/>
+      <c r="I5" s="149">
         <f t="shared" ref="I5:I24" si="0">SUM(F5*H5)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="134"/>
-      <c r="K5" s="135"/>
+      <c r="J5" s="148"/>
+      <c r="K5" s="80"/>
     </row>
     <row r="6" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="136"/>
-      <c r="B6" s="137"/>
-      <c r="C6" s="138"/>
-      <c r="D6" s="139"/>
-      <c r="E6" s="129"/>
-      <c r="F6" s="130"/>
-      <c r="G6" s="131"/>
-      <c r="H6" s="132"/>
-      <c r="I6" s="133">
+      <c r="A6" s="81"/>
+      <c r="B6" s="82"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="149">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J6" s="134"/>
-      <c r="K6" s="135"/>
+      <c r="J6" s="148"/>
+      <c r="K6" s="80"/>
     </row>
     <row r="7" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="136"/>
-      <c r="B7" s="137"/>
-      <c r="C7" s="138"/>
-      <c r="D7" s="139"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="132"/>
-      <c r="I7" s="133">
+      <c r="A7" s="81"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="149">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J7" s="134"/>
-      <c r="K7" s="135"/>
+      <c r="J7" s="148"/>
+      <c r="K7" s="80"/>
     </row>
     <row r="8" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="136"/>
-      <c r="B8" s="137"/>
-      <c r="C8" s="138"/>
-      <c r="D8" s="139"/>
-      <c r="E8" s="141"/>
-      <c r="F8" s="130"/>
-      <c r="G8" s="131"/>
-      <c r="H8" s="132"/>
-      <c r="I8" s="133">
+      <c r="A8" s="81"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="95"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="102"/>
+      <c r="I8" s="149">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="134"/>
-      <c r="K8" s="135"/>
+      <c r="J8" s="148"/>
+      <c r="K8" s="80"/>
     </row>
     <row r="9" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="136"/>
-      <c r="B9" s="137"/>
-      <c r="C9" s="138"/>
-      <c r="D9" s="139"/>
-      <c r="E9" s="141"/>
-      <c r="F9" s="130"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="132"/>
-      <c r="I9" s="133">
+      <c r="A9" s="81"/>
+      <c r="B9" s="82"/>
+      <c r="C9" s="95"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="102"/>
+      <c r="I9" s="149">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="134"/>
-      <c r="K9" s="135"/>
+      <c r="J9" s="148"/>
+      <c r="K9" s="80"/>
     </row>
     <row r="10" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="136"/>
-      <c r="B10" s="137"/>
-      <c r="C10" s="138"/>
-      <c r="D10" s="139"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="130"/>
-      <c r="G10" s="131"/>
-      <c r="H10" s="132"/>
-      <c r="I10" s="133">
+      <c r="A10" s="81"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="95"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="149">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="134"/>
-      <c r="K10" s="135"/>
+      <c r="J10" s="148"/>
+      <c r="K10" s="80"/>
     </row>
     <row r="11" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="136"/>
-      <c r="B11" s="137"/>
-      <c r="C11" s="138"/>
-      <c r="D11" s="139"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="130"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="132"/>
-      <c r="I11" s="133">
+      <c r="A11" s="81"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="102"/>
+      <c r="I11" s="149">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="134"/>
-      <c r="K11" s="135"/>
+      <c r="J11" s="148"/>
+      <c r="K11" s="80"/>
     </row>
     <row r="12" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="136"/>
-      <c r="B12" s="137"/>
-      <c r="C12" s="138"/>
-      <c r="D12" s="139"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="130"/>
-      <c r="G12" s="131"/>
-      <c r="H12" s="132"/>
-      <c r="I12" s="133">
+      <c r="A12" s="81"/>
+      <c r="B12" s="82"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="102"/>
+      <c r="I12" s="149">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="134"/>
-      <c r="K12" s="135"/>
+      <c r="J12" s="148"/>
+      <c r="K12" s="80"/>
     </row>
     <row r="13" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="136"/>
-      <c r="B13" s="137"/>
-      <c r="C13" s="138"/>
-      <c r="D13" s="139"/>
-      <c r="E13" s="129"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="131"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="133">
+      <c r="A13" s="81"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="102"/>
+      <c r="I13" s="149">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="134"/>
-      <c r="K13" s="135"/>
+      <c r="J13" s="148"/>
+      <c r="K13" s="80"/>
     </row>
     <row r="14" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="136"/>
-      <c r="B14" s="137"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="139"/>
-      <c r="E14" s="129"/>
-      <c r="F14" s="130"/>
-      <c r="G14" s="131"/>
-      <c r="H14" s="132"/>
-      <c r="I14" s="133">
+      <c r="A14" s="81"/>
+      <c r="B14" s="82"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="104"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="102"/>
+      <c r="I14" s="149">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="134"/>
-      <c r="K14" s="135"/>
+      <c r="J14" s="148"/>
+      <c r="K14" s="80"/>
     </row>
     <row r="15" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="136"/>
-      <c r="B15" s="137"/>
-      <c r="C15" s="138"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="141"/>
-      <c r="F15" s="130"/>
-      <c r="G15" s="131"/>
-      <c r="H15" s="142"/>
-      <c r="I15" s="143">
+      <c r="A15" s="81"/>
+      <c r="B15" s="82"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="97"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="147">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="134"/>
-      <c r="K15" s="135"/>
+      <c r="J15" s="148"/>
+      <c r="K15" s="80"/>
     </row>
     <row r="16" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="136"/>
-      <c r="B16" s="137"/>
-      <c r="C16" s="138"/>
-      <c r="D16" s="139"/>
-      <c r="E16" s="141"/>
-      <c r="F16" s="130"/>
-      <c r="G16" s="131"/>
-      <c r="H16" s="144"/>
-      <c r="I16" s="143">
+      <c r="A16" s="81"/>
+      <c r="B16" s="82"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="97"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="104"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="103"/>
+      <c r="I16" s="147">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="134"/>
-      <c r="K16" s="135"/>
+      <c r="J16" s="148"/>
+      <c r="K16" s="80"/>
     </row>
     <row r="17" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="136"/>
-      <c r="B17" s="137"/>
-      <c r="C17" s="138"/>
-      <c r="D17" s="139"/>
-      <c r="E17" s="141"/>
-      <c r="F17" s="130"/>
-      <c r="G17" s="131"/>
-      <c r="H17" s="144"/>
-      <c r="I17" s="143">
+      <c r="A17" s="81"/>
+      <c r="B17" s="82"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="97"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="147">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="134"/>
-      <c r="K17" s="135"/>
+      <c r="J17" s="148"/>
+      <c r="K17" s="80"/>
     </row>
     <row r="18" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="136"/>
-      <c r="B18" s="137"/>
-      <c r="C18" s="138"/>
-      <c r="D18" s="139"/>
-      <c r="E18" s="141"/>
-      <c r="F18" s="130"/>
-      <c r="G18" s="131"/>
-      <c r="H18" s="132"/>
-      <c r="I18" s="133">
+      <c r="A18" s="81"/>
+      <c r="B18" s="82"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="104"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="102"/>
+      <c r="I18" s="149">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="134"/>
-      <c r="K18" s="135"/>
+      <c r="J18" s="148"/>
+      <c r="K18" s="80"/>
     </row>
     <row r="19" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="136"/>
-      <c r="B19" s="137"/>
-      <c r="C19" s="138"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="130"/>
-      <c r="G19" s="131"/>
-      <c r="H19" s="132"/>
-      <c r="I19" s="133">
+      <c r="A19" s="81"/>
+      <c r="B19" s="82"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="97"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="102"/>
+      <c r="I19" s="149">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="134"/>
-      <c r="K19" s="135"/>
+      <c r="J19" s="148"/>
+      <c r="K19" s="80"/>
     </row>
     <row r="20" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="136"/>
-      <c r="B20" s="137"/>
-      <c r="C20" s="138"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="129"/>
-      <c r="F20" s="130"/>
-      <c r="G20" s="131"/>
-      <c r="H20" s="132"/>
-      <c r="I20" s="133">
+      <c r="A20" s="81"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="97"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="104"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="102"/>
+      <c r="I20" s="149">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J20" s="134"/>
-      <c r="K20" s="135"/>
+      <c r="J20" s="148"/>
+      <c r="K20" s="80"/>
     </row>
     <row r="21" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="136"/>
-      <c r="B21" s="137"/>
-      <c r="C21" s="138"/>
-      <c r="D21" s="139"/>
-      <c r="E21" s="129"/>
-      <c r="F21" s="130"/>
-      <c r="G21" s="131"/>
-      <c r="H21" s="132"/>
-      <c r="I21" s="133">
+      <c r="A21" s="81"/>
+      <c r="B21" s="82"/>
+      <c r="C21" s="95"/>
+      <c r="D21" s="97"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="102"/>
+      <c r="I21" s="149">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="134"/>
-      <c r="K21" s="135"/>
+      <c r="J21" s="148"/>
+      <c r="K21" s="80"/>
     </row>
     <row r="22" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="136"/>
-      <c r="B22" s="137"/>
-      <c r="C22" s="138"/>
-      <c r="D22" s="139"/>
-      <c r="E22" s="129"/>
-      <c r="F22" s="130"/>
-      <c r="G22" s="131"/>
-      <c r="H22" s="132"/>
-      <c r="I22" s="133">
+      <c r="A22" s="81"/>
+      <c r="B22" s="82"/>
+      <c r="C22" s="95"/>
+      <c r="D22" s="97"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="104"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="102"/>
+      <c r="I22" s="149">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="134"/>
-      <c r="K22" s="135"/>
+      <c r="J22" s="148"/>
+      <c r="K22" s="80"/>
     </row>
     <row r="23" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="136"/>
-      <c r="B23" s="137"/>
-      <c r="C23" s="138"/>
-      <c r="D23" s="139"/>
-      <c r="E23" s="145"/>
-      <c r="F23" s="130"/>
-      <c r="G23" s="131"/>
-      <c r="H23" s="132"/>
-      <c r="I23" s="133">
+      <c r="A23" s="81"/>
+      <c r="B23" s="82"/>
+      <c r="C23" s="95"/>
+      <c r="D23" s="97"/>
+      <c r="E23" s="98"/>
+      <c r="F23" s="104"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="102"/>
+      <c r="I23" s="149">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J23" s="134"/>
-      <c r="K23" s="135"/>
+      <c r="J23" s="148"/>
+      <c r="K23" s="80"/>
     </row>
     <row r="24" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="136"/>
-      <c r="B24" s="137"/>
-      <c r="C24" s="138"/>
-      <c r="D24" s="139"/>
-      <c r="E24" s="129"/>
-      <c r="F24" s="130"/>
-      <c r="G24" s="131"/>
-      <c r="H24" s="132"/>
-      <c r="I24" s="133">
+      <c r="A24" s="81"/>
+      <c r="B24" s="82"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="97"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="102"/>
+      <c r="I24" s="149">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J24" s="134"/>
-      <c r="K24" s="135"/>
+      <c r="J24" s="148"/>
+      <c r="K24" s="80"/>
     </row>
     <row r="25" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="146"/>
-      <c r="B25" s="147"/>
-      <c r="C25" s="148" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="149"/>
-      <c r="E25" s="150"/>
-      <c r="F25" s="150"/>
-      <c r="G25" s="151"/>
-      <c r="H25" s="132"/>
-      <c r="I25" s="133">
+      <c r="A25" s="101"/>
+      <c r="B25" s="84"/>
+      <c r="C25" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="84"/>
+      <c r="E25" s="99"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="102"/>
+      <c r="I25" s="149">
         <f>SUM(I2:J24)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="134"/>
-      <c r="K25" s="152"/>
+      <c r="J25" s="148"/>
+      <c r="K25" s="85"/>
     </row>
     <row r="26" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="114" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" s="114"/>
-      <c r="C26" s="115">
+      <c r="A26" s="141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="141"/>
+      <c r="C26" s="142">
         <f>表紙!C40</f>
         <v>0</v>
       </c>
-      <c r="D26" s="115"/>
-      <c r="E26" s="115"/>
-      <c r="F26" s="116" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" s="116"/>
-      <c r="H26" s="116"/>
-      <c r="I26" s="116"/>
-      <c r="J26" s="114" t="s">
-        <v>83</v>
-      </c>
-      <c r="K26" s="114"/>
+      <c r="D26" s="142"/>
+      <c r="E26" s="142"/>
+      <c r="F26" s="143" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="143"/>
+      <c r="H26" s="143"/>
+      <c r="I26" s="143"/>
+      <c r="J26" s="144" t="s">
+        <v>82</v>
+      </c>
+      <c r="K26" s="144"/>
     </row>
     <row r="27" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="117"/>
-      <c r="B27" s="118" t="s">
+      <c r="A27" s="73"/>
+      <c r="B27" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="119"/>
-      <c r="D27" s="120" t="s">
+      <c r="C27" s="75"/>
+      <c r="D27" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="E27" s="121"/>
-      <c r="F27" s="122" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="122" t="s">
+      <c r="E27" s="77"/>
+      <c r="F27" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="H27" s="122" t="s">
+      <c r="H27" s="78" t="s">
+        <v>88</v>
+      </c>
+      <c r="I27" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="I27" s="123" t="s">
+      <c r="J27" s="146"/>
+      <c r="K27" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="J27" s="124"/>
-      <c r="K27" s="122" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="28" spans="1:11" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="125"/>
-      <c r="B28" s="126"/>
-      <c r="C28" s="127"/>
-      <c r="D28" s="128"/>
-      <c r="E28" s="129"/>
-      <c r="F28" s="130"/>
-      <c r="G28" s="131"/>
-      <c r="H28" s="132"/>
-      <c r="I28" s="133">
+      <c r="A28" s="100"/>
+      <c r="B28" s="93"/>
+      <c r="C28" s="94"/>
+      <c r="D28" s="96"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="104"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="102"/>
+      <c r="I28" s="149">
         <f>SUM(F28*H28)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="134"/>
-      <c r="K28" s="135"/>
+      <c r="J28" s="148"/>
+      <c r="K28" s="80"/>
     </row>
     <row r="29" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="136"/>
-      <c r="B29" s="137"/>
-      <c r="C29" s="138"/>
-      <c r="D29" s="139"/>
-      <c r="E29" s="129"/>
-      <c r="F29" s="130"/>
-      <c r="G29" s="131"/>
-      <c r="H29" s="132"/>
-      <c r="I29" s="133">
+      <c r="A29" s="81"/>
+      <c r="B29" s="82"/>
+      <c r="C29" s="95"/>
+      <c r="D29" s="97"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="104"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="102"/>
+      <c r="I29" s="149">
         <f>SUM(F29*H29)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="134"/>
-      <c r="K29" s="135"/>
+      <c r="J29" s="148"/>
+      <c r="K29" s="80"/>
     </row>
     <row r="30" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="136"/>
-      <c r="B30" s="140"/>
-      <c r="C30" s="138"/>
-      <c r="D30" s="139"/>
-      <c r="E30" s="129"/>
-      <c r="F30" s="130"/>
-      <c r="G30" s="131"/>
-      <c r="H30" s="132"/>
-      <c r="I30" s="133">
+      <c r="A30" s="81"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="95"/>
+      <c r="D30" s="97"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="104"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="102"/>
+      <c r="I30" s="149">
         <f t="shared" ref="I30:I49" si="1">SUM(F30*H30)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="134"/>
-      <c r="K30" s="135"/>
+      <c r="J30" s="148"/>
+      <c r="K30" s="80"/>
     </row>
     <row r="31" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="136"/>
-      <c r="B31" s="137"/>
-      <c r="C31" s="138"/>
-      <c r="D31" s="139"/>
-      <c r="E31" s="129"/>
-      <c r="F31" s="130"/>
-      <c r="G31" s="131"/>
-      <c r="H31" s="132"/>
-      <c r="I31" s="133">
+      <c r="A31" s="81"/>
+      <c r="B31" s="82"/>
+      <c r="C31" s="95"/>
+      <c r="D31" s="97"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="102"/>
+      <c r="I31" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J31" s="134"/>
-      <c r="K31" s="135"/>
+      <c r="J31" s="148"/>
+      <c r="K31" s="80"/>
     </row>
     <row r="32" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="136"/>
-      <c r="B32" s="137"/>
-      <c r="C32" s="138"/>
-      <c r="D32" s="139"/>
-      <c r="E32" s="129"/>
-      <c r="F32" s="130"/>
-      <c r="G32" s="131"/>
-      <c r="H32" s="132"/>
-      <c r="I32" s="133">
+      <c r="A32" s="81"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="95"/>
+      <c r="D32" s="97"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="104"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="102"/>
+      <c r="I32" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J32" s="134"/>
-      <c r="K32" s="135"/>
+      <c r="J32" s="148"/>
+      <c r="K32" s="80"/>
     </row>
     <row r="33" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="136"/>
-      <c r="B33" s="137"/>
-      <c r="C33" s="138"/>
-      <c r="D33" s="139"/>
-      <c r="E33" s="141"/>
-      <c r="F33" s="130"/>
-      <c r="G33" s="131"/>
-      <c r="H33" s="132"/>
-      <c r="I33" s="133">
+      <c r="A33" s="81"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="95"/>
+      <c r="D33" s="97"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="102"/>
+      <c r="I33" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J33" s="134"/>
-      <c r="K33" s="135"/>
+      <c r="J33" s="148"/>
+      <c r="K33" s="80"/>
     </row>
     <row r="34" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="136"/>
-      <c r="B34" s="137"/>
-      <c r="C34" s="138"/>
-      <c r="D34" s="139"/>
-      <c r="E34" s="141"/>
-      <c r="F34" s="130"/>
-      <c r="G34" s="131"/>
-      <c r="H34" s="132"/>
-      <c r="I34" s="133">
+      <c r="A34" s="81"/>
+      <c r="B34" s="82"/>
+      <c r="C34" s="95"/>
+      <c r="D34" s="97"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="104"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="102"/>
+      <c r="I34" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J34" s="134"/>
-      <c r="K34" s="135"/>
+      <c r="J34" s="148"/>
+      <c r="K34" s="80"/>
     </row>
     <row r="35" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="136"/>
-      <c r="B35" s="137"/>
-      <c r="C35" s="138"/>
-      <c r="D35" s="139"/>
-      <c r="E35" s="129"/>
-      <c r="F35" s="130"/>
-      <c r="G35" s="131"/>
-      <c r="H35" s="132"/>
-      <c r="I35" s="133">
+      <c r="A35" s="81"/>
+      <c r="B35" s="82"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="97"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="104"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="102"/>
+      <c r="I35" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J35" s="134"/>
-      <c r="K35" s="135"/>
+      <c r="J35" s="148"/>
+      <c r="K35" s="80"/>
     </row>
     <row r="36" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="136"/>
-      <c r="B36" s="137"/>
-      <c r="C36" s="138"/>
-      <c r="D36" s="139"/>
-      <c r="E36" s="129"/>
-      <c r="F36" s="130"/>
-      <c r="G36" s="131"/>
-      <c r="H36" s="132"/>
-      <c r="I36" s="133">
+      <c r="A36" s="81"/>
+      <c r="B36" s="82"/>
+      <c r="C36" s="95"/>
+      <c r="D36" s="97"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="104"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="102"/>
+      <c r="I36" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J36" s="134"/>
-      <c r="K36" s="135"/>
+      <c r="J36" s="148"/>
+      <c r="K36" s="80"/>
     </row>
     <row r="37" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="136"/>
-      <c r="B37" s="137"/>
-      <c r="C37" s="138"/>
-      <c r="D37" s="139"/>
-      <c r="E37" s="129"/>
-      <c r="F37" s="130"/>
-      <c r="G37" s="131"/>
-      <c r="H37" s="132"/>
-      <c r="I37" s="133">
+      <c r="A37" s="81"/>
+      <c r="B37" s="82"/>
+      <c r="C37" s="95"/>
+      <c r="D37" s="97"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="102"/>
+      <c r="I37" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J37" s="134"/>
-      <c r="K37" s="135"/>
+      <c r="J37" s="148"/>
+      <c r="K37" s="80"/>
     </row>
     <row r="38" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="136"/>
-      <c r="B38" s="137"/>
-      <c r="C38" s="138"/>
-      <c r="D38" s="139"/>
-      <c r="E38" s="129"/>
-      <c r="F38" s="130"/>
-      <c r="G38" s="131"/>
-      <c r="H38" s="132"/>
-      <c r="I38" s="133">
+      <c r="A38" s="81"/>
+      <c r="B38" s="82"/>
+      <c r="C38" s="95"/>
+      <c r="D38" s="97"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="104"/>
+      <c r="G38" s="34"/>
+      <c r="H38" s="102"/>
+      <c r="I38" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J38" s="134"/>
-      <c r="K38" s="135"/>
+      <c r="J38" s="148"/>
+      <c r="K38" s="80"/>
     </row>
     <row r="39" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="136"/>
-      <c r="B39" s="137"/>
-      <c r="C39" s="138"/>
-      <c r="D39" s="139"/>
-      <c r="E39" s="129"/>
-      <c r="F39" s="130"/>
-      <c r="G39" s="131"/>
-      <c r="H39" s="132"/>
-      <c r="I39" s="133">
+      <c r="A39" s="81"/>
+      <c r="B39" s="82"/>
+      <c r="C39" s="95"/>
+      <c r="D39" s="97"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="104"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="102"/>
+      <c r="I39" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J39" s="134"/>
-      <c r="K39" s="135"/>
+      <c r="J39" s="148"/>
+      <c r="K39" s="80"/>
     </row>
     <row r="40" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="136"/>
-      <c r="B40" s="137"/>
-      <c r="C40" s="138"/>
-      <c r="D40" s="139"/>
-      <c r="E40" s="141"/>
-      <c r="F40" s="130"/>
-      <c r="G40" s="131"/>
-      <c r="H40" s="142"/>
-      <c r="I40" s="143">
+      <c r="A40" s="81"/>
+      <c r="B40" s="82"/>
+      <c r="C40" s="95"/>
+      <c r="D40" s="97"/>
+      <c r="E40" s="83"/>
+      <c r="F40" s="104"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J40" s="134"/>
-      <c r="K40" s="135"/>
+      <c r="J40" s="148"/>
+      <c r="K40" s="80"/>
     </row>
     <row r="41" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="136"/>
-      <c r="B41" s="137"/>
-      <c r="C41" s="138"/>
-      <c r="D41" s="139"/>
-      <c r="E41" s="141"/>
-      <c r="F41" s="130"/>
-      <c r="G41" s="131"/>
-      <c r="H41" s="144"/>
-      <c r="I41" s="143">
+      <c r="A41" s="81"/>
+      <c r="B41" s="82"/>
+      <c r="C41" s="95"/>
+      <c r="D41" s="97"/>
+      <c r="E41" s="83"/>
+      <c r="F41" s="104"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J41" s="134"/>
-      <c r="K41" s="135"/>
+      <c r="J41" s="148"/>
+      <c r="K41" s="80"/>
     </row>
     <row r="42" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="136"/>
-      <c r="B42" s="137"/>
-      <c r="C42" s="138"/>
-      <c r="D42" s="139"/>
-      <c r="E42" s="141"/>
-      <c r="F42" s="130"/>
-      <c r="G42" s="131"/>
-      <c r="H42" s="144"/>
-      <c r="I42" s="143">
+      <c r="A42" s="81"/>
+      <c r="B42" s="82"/>
+      <c r="C42" s="95"/>
+      <c r="D42" s="97"/>
+      <c r="E42" s="83"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J42" s="134"/>
-      <c r="K42" s="135"/>
+      <c r="J42" s="148"/>
+      <c r="K42" s="80"/>
     </row>
     <row r="43" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="136"/>
-      <c r="B43" s="137"/>
-      <c r="C43" s="138"/>
-      <c r="D43" s="139"/>
-      <c r="E43" s="141"/>
-      <c r="F43" s="130"/>
-      <c r="G43" s="131"/>
-      <c r="H43" s="132"/>
-      <c r="I43" s="133">
+      <c r="A43" s="81"/>
+      <c r="B43" s="82"/>
+      <c r="C43" s="95"/>
+      <c r="D43" s="97"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="104"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="102"/>
+      <c r="I43" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J43" s="134"/>
-      <c r="K43" s="135"/>
+      <c r="J43" s="148"/>
+      <c r="K43" s="80"/>
     </row>
     <row r="44" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="136"/>
-      <c r="B44" s="137"/>
-      <c r="C44" s="138"/>
-      <c r="D44" s="139"/>
-      <c r="E44" s="129"/>
-      <c r="F44" s="130"/>
-      <c r="G44" s="131"/>
-      <c r="H44" s="132"/>
-      <c r="I44" s="133">
+      <c r="A44" s="81"/>
+      <c r="B44" s="82"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="97"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="104"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="102"/>
+      <c r="I44" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J44" s="134"/>
-      <c r="K44" s="135"/>
+      <c r="J44" s="148"/>
+      <c r="K44" s="80"/>
     </row>
     <row r="45" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="136"/>
-      <c r="B45" s="137"/>
-      <c r="C45" s="138"/>
-      <c r="D45" s="139"/>
-      <c r="E45" s="129"/>
-      <c r="F45" s="130"/>
-      <c r="G45" s="131"/>
-      <c r="H45" s="132"/>
-      <c r="I45" s="133">
+      <c r="A45" s="81"/>
+      <c r="B45" s="82"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="97"/>
+      <c r="E45" s="83"/>
+      <c r="F45" s="104"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="102"/>
+      <c r="I45" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J45" s="134"/>
-      <c r="K45" s="135"/>
+      <c r="J45" s="148"/>
+      <c r="K45" s="80"/>
     </row>
     <row r="46" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="136"/>
-      <c r="B46" s="137"/>
-      <c r="C46" s="138"/>
-      <c r="D46" s="139"/>
-      <c r="E46" s="129"/>
-      <c r="F46" s="130"/>
-      <c r="G46" s="131"/>
-      <c r="H46" s="132"/>
-      <c r="I46" s="133">
+      <c r="A46" s="81"/>
+      <c r="B46" s="82"/>
+      <c r="C46" s="95"/>
+      <c r="D46" s="97"/>
+      <c r="E46" s="83"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="34"/>
+      <c r="H46" s="102"/>
+      <c r="I46" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J46" s="134"/>
-      <c r="K46" s="135"/>
+      <c r="J46" s="148"/>
+      <c r="K46" s="80"/>
     </row>
     <row r="47" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="136"/>
-      <c r="B47" s="137"/>
-      <c r="C47" s="138"/>
-      <c r="D47" s="139"/>
-      <c r="E47" s="129"/>
-      <c r="F47" s="130"/>
-      <c r="G47" s="131"/>
-      <c r="H47" s="132"/>
-      <c r="I47" s="133">
+      <c r="A47" s="81"/>
+      <c r="B47" s="82"/>
+      <c r="C47" s="95"/>
+      <c r="D47" s="97"/>
+      <c r="E47" s="83"/>
+      <c r="F47" s="104"/>
+      <c r="G47" s="34"/>
+      <c r="H47" s="102"/>
+      <c r="I47" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J47" s="134"/>
-      <c r="K47" s="135"/>
+      <c r="J47" s="148"/>
+      <c r="K47" s="80"/>
     </row>
     <row r="48" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="136"/>
-      <c r="B48" s="137"/>
-      <c r="C48" s="138"/>
-      <c r="D48" s="139"/>
-      <c r="E48" s="145"/>
-      <c r="F48" s="130"/>
-      <c r="G48" s="131"/>
-      <c r="H48" s="132"/>
-      <c r="I48" s="133">
+      <c r="A48" s="81"/>
+      <c r="B48" s="82"/>
+      <c r="C48" s="95"/>
+      <c r="D48" s="97"/>
+      <c r="E48" s="98"/>
+      <c r="F48" s="104"/>
+      <c r="G48" s="34"/>
+      <c r="H48" s="102"/>
+      <c r="I48" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J48" s="134"/>
-      <c r="K48" s="135"/>
+      <c r="J48" s="148"/>
+      <c r="K48" s="80"/>
     </row>
     <row r="49" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="136"/>
-      <c r="B49" s="137"/>
-      <c r="C49" s="138"/>
-      <c r="D49" s="139"/>
-      <c r="E49" s="129"/>
-      <c r="F49" s="130"/>
-      <c r="G49" s="131"/>
-      <c r="H49" s="132"/>
-      <c r="I49" s="133">
+      <c r="A49" s="81"/>
+      <c r="B49" s="82"/>
+      <c r="C49" s="95"/>
+      <c r="D49" s="97"/>
+      <c r="E49" s="83"/>
+      <c r="F49" s="104"/>
+      <c r="G49" s="34"/>
+      <c r="H49" s="102"/>
+      <c r="I49" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J49" s="134"/>
-      <c r="K49" s="135"/>
+      <c r="J49" s="148"/>
+      <c r="K49" s="80"/>
     </row>
     <row r="50" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="146"/>
-      <c r="B50" s="147"/>
-      <c r="C50" s="148" t="s">
-        <v>18</v>
-      </c>
-      <c r="D50" s="149"/>
-      <c r="E50" s="150"/>
-      <c r="F50" s="150"/>
-      <c r="G50" s="151"/>
-      <c r="H50" s="132"/>
-      <c r="I50" s="133">
+      <c r="A50" s="101"/>
+      <c r="B50" s="84"/>
+      <c r="C50" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="84"/>
+      <c r="E50" s="99"/>
+      <c r="F50" s="105"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="102"/>
+      <c r="I50" s="149">
         <f>SUM(I27:J49)</f>
         <v>0</v>
       </c>
-      <c r="J50" s="134"/>
-      <c r="K50" s="152"/>
+      <c r="J50" s="148"/>
+      <c r="K50" s="85"/>
     </row>
     <row r="51" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="114" t="s">
-        <v>16</v>
-      </c>
-      <c r="B51" s="114"/>
-      <c r="C51" s="115">
+      <c r="A51" s="141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" s="141"/>
+      <c r="C51" s="142">
         <f>表紙!C65</f>
         <v>0</v>
       </c>
-      <c r="D51" s="115"/>
-      <c r="E51" s="115"/>
-      <c r="F51" s="116" t="s">
-        <v>17</v>
-      </c>
-      <c r="G51" s="116"/>
-      <c r="H51" s="116"/>
-      <c r="I51" s="116"/>
-      <c r="J51" s="114" t="s">
-        <v>84</v>
-      </c>
-      <c r="K51" s="114"/>
+      <c r="D51" s="142"/>
+      <c r="E51" s="142"/>
+      <c r="F51" s="143" t="s">
+        <v>16</v>
+      </c>
+      <c r="G51" s="143"/>
+      <c r="H51" s="143"/>
+      <c r="I51" s="143"/>
+      <c r="J51" s="144" t="s">
+        <v>83</v>
+      </c>
+      <c r="K51" s="144"/>
     </row>
     <row r="52" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="117"/>
-      <c r="B52" s="118" t="s">
+      <c r="A52" s="73"/>
+      <c r="B52" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="119"/>
-      <c r="D52" s="120" t="s">
+      <c r="C52" s="75"/>
+      <c r="D52" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="121"/>
-      <c r="F52" s="122" t="s">
-        <v>82</v>
-      </c>
-      <c r="G52" s="122" t="s">
+      <c r="E52" s="77"/>
+      <c r="F52" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="G52" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="H52" s="122" t="s">
+      <c r="H52" s="78" t="s">
+        <v>88</v>
+      </c>
+      <c r="I52" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="I52" s="123" t="s">
+      <c r="J52" s="146"/>
+      <c r="K52" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="J52" s="124"/>
-      <c r="K52" s="122" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="53" spans="1:11" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="125"/>
-      <c r="B53" s="126"/>
-      <c r="C53" s="127"/>
-      <c r="D53" s="128"/>
-      <c r="E53" s="129"/>
-      <c r="F53" s="130"/>
-      <c r="G53" s="131"/>
-      <c r="H53" s="132"/>
-      <c r="I53" s="133">
+      <c r="A53" s="100"/>
+      <c r="B53" s="93"/>
+      <c r="C53" s="94"/>
+      <c r="D53" s="96"/>
+      <c r="E53" s="83"/>
+      <c r="F53" s="104"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="102"/>
+      <c r="I53" s="149">
         <f>SUM(F53*H53)</f>
         <v>0</v>
       </c>
-      <c r="J53" s="134"/>
-      <c r="K53" s="135"/>
+      <c r="J53" s="148"/>
+      <c r="K53" s="80"/>
     </row>
     <row r="54" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="136"/>
-      <c r="B54" s="137"/>
-      <c r="C54" s="138"/>
-      <c r="D54" s="139"/>
-      <c r="E54" s="129"/>
-      <c r="F54" s="130"/>
-      <c r="G54" s="131"/>
-      <c r="H54" s="132"/>
-      <c r="I54" s="133">
+      <c r="A54" s="81"/>
+      <c r="B54" s="82"/>
+      <c r="C54" s="95"/>
+      <c r="D54" s="97"/>
+      <c r="E54" s="83"/>
+      <c r="F54" s="104"/>
+      <c r="G54" s="34"/>
+      <c r="H54" s="102"/>
+      <c r="I54" s="149">
         <f>SUM(F54*H54)</f>
         <v>0</v>
       </c>
-      <c r="J54" s="134"/>
-      <c r="K54" s="135"/>
+      <c r="J54" s="148"/>
+      <c r="K54" s="80"/>
     </row>
     <row r="55" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="136"/>
-      <c r="B55" s="140"/>
-      <c r="C55" s="138"/>
-      <c r="D55" s="139"/>
-      <c r="E55" s="129"/>
-      <c r="F55" s="130"/>
-      <c r="G55" s="131"/>
-      <c r="H55" s="132"/>
-      <c r="I55" s="133">
+      <c r="A55" s="81"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="95"/>
+      <c r="D55" s="97"/>
+      <c r="E55" s="83"/>
+      <c r="F55" s="104"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="102"/>
+      <c r="I55" s="149">
         <f t="shared" ref="I55:I74" si="2">SUM(F55*H55)</f>
         <v>0</v>
       </c>
-      <c r="J55" s="134"/>
-      <c r="K55" s="135"/>
+      <c r="J55" s="148"/>
+      <c r="K55" s="80"/>
     </row>
     <row r="56" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="136"/>
-      <c r="B56" s="137"/>
-      <c r="C56" s="138"/>
-      <c r="D56" s="139"/>
-      <c r="E56" s="129"/>
-      <c r="F56" s="130"/>
-      <c r="G56" s="131"/>
-      <c r="H56" s="132"/>
-      <c r="I56" s="133">
+      <c r="A56" s="81"/>
+      <c r="B56" s="82"/>
+      <c r="C56" s="95"/>
+      <c r="D56" s="97"/>
+      <c r="E56" s="83"/>
+      <c r="F56" s="104"/>
+      <c r="G56" s="34"/>
+      <c r="H56" s="102"/>
+      <c r="I56" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J56" s="134"/>
-      <c r="K56" s="135"/>
+      <c r="J56" s="148"/>
+      <c r="K56" s="80"/>
     </row>
     <row r="57" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="136"/>
-      <c r="B57" s="137"/>
-      <c r="C57" s="138"/>
-      <c r="D57" s="139"/>
-      <c r="E57" s="129"/>
-      <c r="F57" s="130"/>
-      <c r="G57" s="131"/>
-      <c r="H57" s="132"/>
-      <c r="I57" s="133">
+      <c r="A57" s="81"/>
+      <c r="B57" s="82"/>
+      <c r="C57" s="95"/>
+      <c r="D57" s="97"/>
+      <c r="E57" s="83"/>
+      <c r="F57" s="104"/>
+      <c r="G57" s="34"/>
+      <c r="H57" s="102"/>
+      <c r="I57" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J57" s="134"/>
-      <c r="K57" s="135"/>
+      <c r="J57" s="148"/>
+      <c r="K57" s="80"/>
     </row>
     <row r="58" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="136"/>
-      <c r="B58" s="137"/>
-      <c r="C58" s="138"/>
-      <c r="D58" s="139"/>
-      <c r="E58" s="141"/>
-      <c r="F58" s="130"/>
-      <c r="G58" s="131"/>
-      <c r="H58" s="132"/>
-      <c r="I58" s="133">
+      <c r="A58" s="81"/>
+      <c r="B58" s="82"/>
+      <c r="C58" s="95"/>
+      <c r="D58" s="97"/>
+      <c r="E58" s="83"/>
+      <c r="F58" s="104"/>
+      <c r="G58" s="34"/>
+      <c r="H58" s="102"/>
+      <c r="I58" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J58" s="134"/>
-      <c r="K58" s="135"/>
+      <c r="J58" s="148"/>
+      <c r="K58" s="80"/>
     </row>
     <row r="59" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="136"/>
-      <c r="B59" s="137"/>
-      <c r="C59" s="138"/>
-      <c r="D59" s="139"/>
-      <c r="E59" s="141"/>
-      <c r="F59" s="130"/>
-      <c r="G59" s="131"/>
-      <c r="H59" s="132"/>
-      <c r="I59" s="133">
+      <c r="A59" s="81"/>
+      <c r="B59" s="82"/>
+      <c r="C59" s="95"/>
+      <c r="D59" s="97"/>
+      <c r="E59" s="83"/>
+      <c r="F59" s="104"/>
+      <c r="G59" s="34"/>
+      <c r="H59" s="102"/>
+      <c r="I59" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J59" s="134"/>
-      <c r="K59" s="135"/>
+      <c r="J59" s="148"/>
+      <c r="K59" s="80"/>
     </row>
     <row r="60" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="136"/>
-      <c r="B60" s="137"/>
-      <c r="C60" s="138"/>
-      <c r="D60" s="139"/>
-      <c r="E60" s="129"/>
-      <c r="F60" s="130"/>
-      <c r="G60" s="131"/>
-      <c r="H60" s="132"/>
-      <c r="I60" s="133">
+      <c r="A60" s="81"/>
+      <c r="B60" s="82"/>
+      <c r="C60" s="95"/>
+      <c r="D60" s="97"/>
+      <c r="E60" s="83"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="34"/>
+      <c r="H60" s="102"/>
+      <c r="I60" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J60" s="134"/>
-      <c r="K60" s="135"/>
+      <c r="J60" s="148"/>
+      <c r="K60" s="80"/>
     </row>
     <row r="61" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="136"/>
-      <c r="B61" s="137"/>
-      <c r="C61" s="138"/>
-      <c r="D61" s="139"/>
-      <c r="E61" s="129"/>
-      <c r="F61" s="130"/>
-      <c r="G61" s="131"/>
-      <c r="H61" s="132"/>
-      <c r="I61" s="133">
+      <c r="A61" s="81"/>
+      <c r="B61" s="82"/>
+      <c r="C61" s="95"/>
+      <c r="D61" s="97"/>
+      <c r="E61" s="83"/>
+      <c r="F61" s="104"/>
+      <c r="G61" s="34"/>
+      <c r="H61" s="102"/>
+      <c r="I61" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J61" s="134"/>
-      <c r="K61" s="135"/>
+      <c r="J61" s="148"/>
+      <c r="K61" s="80"/>
     </row>
     <row r="62" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="136"/>
-      <c r="B62" s="137"/>
-      <c r="C62" s="138"/>
-      <c r="D62" s="139"/>
-      <c r="E62" s="129"/>
-      <c r="F62" s="130"/>
-      <c r="G62" s="131"/>
-      <c r="H62" s="132"/>
-      <c r="I62" s="133">
+      <c r="A62" s="81"/>
+      <c r="B62" s="82"/>
+      <c r="C62" s="95"/>
+      <c r="D62" s="97"/>
+      <c r="E62" s="83"/>
+      <c r="F62" s="104"/>
+      <c r="G62" s="34"/>
+      <c r="H62" s="102"/>
+      <c r="I62" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J62" s="134"/>
-      <c r="K62" s="135"/>
+      <c r="J62" s="148"/>
+      <c r="K62" s="80"/>
     </row>
     <row r="63" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="136"/>
-      <c r="B63" s="137"/>
-      <c r="C63" s="138"/>
-      <c r="D63" s="139"/>
-      <c r="E63" s="129"/>
-      <c r="F63" s="130"/>
-      <c r="G63" s="131"/>
-      <c r="H63" s="132"/>
-      <c r="I63" s="133">
+      <c r="A63" s="81"/>
+      <c r="B63" s="82"/>
+      <c r="C63" s="95"/>
+      <c r="D63" s="97"/>
+      <c r="E63" s="83"/>
+      <c r="F63" s="104"/>
+      <c r="G63" s="34"/>
+      <c r="H63" s="102"/>
+      <c r="I63" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J63" s="134"/>
-      <c r="K63" s="135"/>
+      <c r="J63" s="148"/>
+      <c r="K63" s="80"/>
     </row>
     <row r="64" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="136"/>
-      <c r="B64" s="137"/>
-      <c r="C64" s="138"/>
-      <c r="D64" s="139"/>
-      <c r="E64" s="129"/>
-      <c r="F64" s="130"/>
-      <c r="G64" s="131"/>
-      <c r="H64" s="132"/>
-      <c r="I64" s="133">
+      <c r="A64" s="81"/>
+      <c r="B64" s="82"/>
+      <c r="C64" s="95"/>
+      <c r="D64" s="97"/>
+      <c r="E64" s="83"/>
+      <c r="F64" s="104"/>
+      <c r="G64" s="34"/>
+      <c r="H64" s="102"/>
+      <c r="I64" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J64" s="134"/>
-      <c r="K64" s="135"/>
+      <c r="J64" s="148"/>
+      <c r="K64" s="80"/>
     </row>
     <row r="65" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="136"/>
-      <c r="B65" s="137"/>
-      <c r="C65" s="138"/>
-      <c r="D65" s="139"/>
-      <c r="E65" s="141"/>
-      <c r="F65" s="130"/>
-      <c r="G65" s="131"/>
-      <c r="H65" s="142"/>
-      <c r="I65" s="143">
+      <c r="A65" s="81"/>
+      <c r="B65" s="82"/>
+      <c r="C65" s="95"/>
+      <c r="D65" s="97"/>
+      <c r="E65" s="83"/>
+      <c r="F65" s="104"/>
+      <c r="G65" s="34"/>
+      <c r="H65" s="103"/>
+      <c r="I65" s="147">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J65" s="134"/>
-      <c r="K65" s="135"/>
+      <c r="J65" s="148"/>
+      <c r="K65" s="80"/>
     </row>
     <row r="66" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="136"/>
-      <c r="B66" s="137"/>
-      <c r="C66" s="138"/>
-      <c r="D66" s="139"/>
-      <c r="E66" s="141"/>
-      <c r="F66" s="130"/>
-      <c r="G66" s="131"/>
-      <c r="H66" s="144"/>
-      <c r="I66" s="143">
+      <c r="A66" s="81"/>
+      <c r="B66" s="82"/>
+      <c r="C66" s="95"/>
+      <c r="D66" s="97"/>
+      <c r="E66" s="83"/>
+      <c r="F66" s="104"/>
+      <c r="G66" s="34"/>
+      <c r="H66" s="103"/>
+      <c r="I66" s="147">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J66" s="134"/>
-      <c r="K66" s="135"/>
+      <c r="J66" s="148"/>
+      <c r="K66" s="80"/>
     </row>
     <row r="67" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A67" s="136"/>
-      <c r="B67" s="137"/>
-      <c r="C67" s="138"/>
-      <c r="D67" s="139"/>
-      <c r="E67" s="141"/>
-      <c r="F67" s="130"/>
-      <c r="G67" s="131"/>
-      <c r="H67" s="144"/>
-      <c r="I67" s="143">
+      <c r="A67" s="81"/>
+      <c r="B67" s="82"/>
+      <c r="C67" s="95"/>
+      <c r="D67" s="97"/>
+      <c r="E67" s="83"/>
+      <c r="F67" s="104"/>
+      <c r="G67" s="34"/>
+      <c r="H67" s="103"/>
+      <c r="I67" s="147">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J67" s="134"/>
-      <c r="K67" s="135"/>
+      <c r="J67" s="148"/>
+      <c r="K67" s="80"/>
     </row>
     <row r="68" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="136"/>
-      <c r="B68" s="137"/>
-      <c r="C68" s="138"/>
-      <c r="D68" s="139"/>
-      <c r="E68" s="141"/>
-      <c r="F68" s="130"/>
-      <c r="G68" s="131"/>
-      <c r="H68" s="132"/>
-      <c r="I68" s="133">
+      <c r="A68" s="81"/>
+      <c r="B68" s="82"/>
+      <c r="C68" s="95"/>
+      <c r="D68" s="97"/>
+      <c r="E68" s="83"/>
+      <c r="F68" s="104"/>
+      <c r="G68" s="34"/>
+      <c r="H68" s="102"/>
+      <c r="I68" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J68" s="134"/>
-      <c r="K68" s="135"/>
+      <c r="J68" s="148"/>
+      <c r="K68" s="80"/>
     </row>
     <row r="69" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="136"/>
-      <c r="B69" s="137"/>
-      <c r="C69" s="138"/>
-      <c r="D69" s="139"/>
-      <c r="E69" s="129"/>
-      <c r="F69" s="130"/>
-      <c r="G69" s="131"/>
-      <c r="H69" s="132"/>
-      <c r="I69" s="133">
+      <c r="A69" s="81"/>
+      <c r="B69" s="82"/>
+      <c r="C69" s="95"/>
+      <c r="D69" s="97"/>
+      <c r="E69" s="83"/>
+      <c r="F69" s="104"/>
+      <c r="G69" s="34"/>
+      <c r="H69" s="102"/>
+      <c r="I69" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J69" s="134"/>
-      <c r="K69" s="135"/>
+      <c r="J69" s="148"/>
+      <c r="K69" s="80"/>
     </row>
     <row r="70" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="136"/>
-      <c r="B70" s="137"/>
-      <c r="C70" s="138"/>
-      <c r="D70" s="139"/>
-      <c r="E70" s="129"/>
-      <c r="F70" s="130"/>
-      <c r="G70" s="131"/>
-      <c r="H70" s="132"/>
-      <c r="I70" s="133">
+      <c r="A70" s="81"/>
+      <c r="B70" s="82"/>
+      <c r="C70" s="95"/>
+      <c r="D70" s="97"/>
+      <c r="E70" s="83"/>
+      <c r="F70" s="104"/>
+      <c r="G70" s="34"/>
+      <c r="H70" s="102"/>
+      <c r="I70" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J70" s="134"/>
-      <c r="K70" s="135"/>
+      <c r="J70" s="148"/>
+      <c r="K70" s="80"/>
     </row>
     <row r="71" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="136"/>
-      <c r="B71" s="137"/>
-      <c r="C71" s="138"/>
-      <c r="D71" s="139"/>
-      <c r="E71" s="129"/>
-      <c r="F71" s="130"/>
-      <c r="G71" s="131"/>
-      <c r="H71" s="132"/>
-      <c r="I71" s="133">
+      <c r="A71" s="81"/>
+      <c r="B71" s="82"/>
+      <c r="C71" s="95"/>
+      <c r="D71" s="97"/>
+      <c r="E71" s="83"/>
+      <c r="F71" s="104"/>
+      <c r="G71" s="34"/>
+      <c r="H71" s="102"/>
+      <c r="I71" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J71" s="134"/>
-      <c r="K71" s="135"/>
+      <c r="J71" s="148"/>
+      <c r="K71" s="80"/>
     </row>
     <row r="72" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="136"/>
-      <c r="B72" s="137"/>
-      <c r="C72" s="138"/>
-      <c r="D72" s="139"/>
-      <c r="E72" s="129"/>
-      <c r="F72" s="130"/>
-      <c r="G72" s="131"/>
-      <c r="H72" s="132"/>
-      <c r="I72" s="133">
+      <c r="A72" s="81"/>
+      <c r="B72" s="82"/>
+      <c r="C72" s="95"/>
+      <c r="D72" s="97"/>
+      <c r="E72" s="83"/>
+      <c r="F72" s="104"/>
+      <c r="G72" s="34"/>
+      <c r="H72" s="102"/>
+      <c r="I72" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J72" s="134"/>
-      <c r="K72" s="135"/>
+      <c r="J72" s="148"/>
+      <c r="K72" s="80"/>
     </row>
     <row r="73" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="136"/>
-      <c r="B73" s="137"/>
-      <c r="C73" s="138"/>
-      <c r="D73" s="139"/>
-      <c r="E73" s="145"/>
-      <c r="F73" s="130"/>
-      <c r="G73" s="131"/>
-      <c r="H73" s="132"/>
-      <c r="I73" s="133">
+      <c r="A73" s="81"/>
+      <c r="B73" s="82"/>
+      <c r="C73" s="95"/>
+      <c r="D73" s="97"/>
+      <c r="E73" s="98"/>
+      <c r="F73" s="104"/>
+      <c r="G73" s="34"/>
+      <c r="H73" s="102"/>
+      <c r="I73" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J73" s="134"/>
-      <c r="K73" s="135"/>
+      <c r="J73" s="148"/>
+      <c r="K73" s="80"/>
     </row>
     <row r="74" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="136"/>
-      <c r="B74" s="137"/>
-      <c r="C74" s="138"/>
-      <c r="D74" s="139"/>
-      <c r="E74" s="129"/>
-      <c r="F74" s="130"/>
-      <c r="G74" s="131"/>
-      <c r="H74" s="132"/>
-      <c r="I74" s="133">
+      <c r="A74" s="81"/>
+      <c r="B74" s="82"/>
+      <c r="C74" s="95"/>
+      <c r="D74" s="97"/>
+      <c r="E74" s="83"/>
+      <c r="F74" s="104"/>
+      <c r="G74" s="34"/>
+      <c r="H74" s="102"/>
+      <c r="I74" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J74" s="134"/>
-      <c r="K74" s="135"/>
+      <c r="J74" s="148"/>
+      <c r="K74" s="80"/>
     </row>
     <row r="75" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="146"/>
-      <c r="B75" s="147"/>
-      <c r="C75" s="148" t="s">
-        <v>18</v>
-      </c>
-      <c r="D75" s="149"/>
-      <c r="E75" s="150"/>
-      <c r="F75" s="150"/>
-      <c r="G75" s="151"/>
-      <c r="H75" s="132"/>
-      <c r="I75" s="133">
+      <c r="A75" s="101"/>
+      <c r="B75" s="84"/>
+      <c r="C75" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" s="84"/>
+      <c r="E75" s="99"/>
+      <c r="F75" s="105"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="102"/>
+      <c r="I75" s="149">
         <f>SUM(I52:J74)</f>
         <v>0</v>
       </c>
-      <c r="J75" s="134"/>
-      <c r="K75" s="152"/>
+      <c r="J75" s="148"/>
+      <c r="K75" s="85"/>
     </row>
     <row r="76" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="114" t="s">
-        <v>16</v>
-      </c>
-      <c r="B76" s="114"/>
-      <c r="C76" s="115">
+      <c r="A76" s="141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" s="141"/>
+      <c r="C76" s="142">
         <f>表紙!C90</f>
         <v>0</v>
       </c>
-      <c r="D76" s="115"/>
-      <c r="E76" s="115"/>
-      <c r="F76" s="116" t="s">
-        <v>17</v>
-      </c>
-      <c r="G76" s="116"/>
-      <c r="H76" s="116"/>
-      <c r="I76" s="116"/>
-      <c r="J76" s="114" t="s">
-        <v>85</v>
-      </c>
-      <c r="K76" s="114"/>
+      <c r="D76" s="142"/>
+      <c r="E76" s="142"/>
+      <c r="F76" s="143" t="s">
+        <v>16</v>
+      </c>
+      <c r="G76" s="143"/>
+      <c r="H76" s="143"/>
+      <c r="I76" s="143"/>
+      <c r="J76" s="144" t="s">
+        <v>84</v>
+      </c>
+      <c r="K76" s="144"/>
     </row>
     <row r="77" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="117"/>
-      <c r="B77" s="118" t="s">
+      <c r="A77" s="73"/>
+      <c r="B77" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C77" s="119"/>
-      <c r="D77" s="120" t="s">
+      <c r="C77" s="75"/>
+      <c r="D77" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="E77" s="121"/>
-      <c r="F77" s="122" t="s">
-        <v>82</v>
-      </c>
-      <c r="G77" s="122" t="s">
+      <c r="E77" s="77"/>
+      <c r="F77" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="G77" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="H77" s="122" t="s">
+      <c r="H77" s="78" t="s">
+        <v>88</v>
+      </c>
+      <c r="I77" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="I77" s="123" t="s">
+      <c r="J77" s="146"/>
+      <c r="K77" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="J77" s="124"/>
-      <c r="K77" s="122" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="78" spans="1:11" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="125"/>
-      <c r="B78" s="126"/>
-      <c r="C78" s="127"/>
-      <c r="D78" s="128"/>
-      <c r="E78" s="129"/>
-      <c r="F78" s="130"/>
-      <c r="G78" s="131"/>
-      <c r="H78" s="132"/>
-      <c r="I78" s="133">
+      <c r="A78" s="100"/>
+      <c r="B78" s="93"/>
+      <c r="C78" s="94"/>
+      <c r="D78" s="96"/>
+      <c r="E78" s="83"/>
+      <c r="F78" s="104"/>
+      <c r="G78" s="34"/>
+      <c r="H78" s="102"/>
+      <c r="I78" s="149">
         <f>SUM(F78*H78)</f>
         <v>0</v>
       </c>
-      <c r="J78" s="134"/>
-      <c r="K78" s="135"/>
+      <c r="J78" s="148"/>
+      <c r="K78" s="80"/>
     </row>
     <row r="79" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="136"/>
-      <c r="B79" s="137"/>
-      <c r="C79" s="138"/>
-      <c r="D79" s="139"/>
-      <c r="E79" s="129"/>
-      <c r="F79" s="130"/>
-      <c r="G79" s="131"/>
-      <c r="H79" s="132"/>
-      <c r="I79" s="133">
+      <c r="A79" s="81"/>
+      <c r="B79" s="82"/>
+      <c r="C79" s="95"/>
+      <c r="D79" s="97"/>
+      <c r="E79" s="83"/>
+      <c r="F79" s="104"/>
+      <c r="G79" s="34"/>
+      <c r="H79" s="102"/>
+      <c r="I79" s="149">
         <f>SUM(F79*H79)</f>
         <v>0</v>
       </c>
-      <c r="J79" s="134"/>
-      <c r="K79" s="135"/>
+      <c r="J79" s="148"/>
+      <c r="K79" s="80"/>
     </row>
     <row r="80" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A80" s="136"/>
-      <c r="B80" s="140"/>
-      <c r="C80" s="138"/>
-      <c r="D80" s="139"/>
-      <c r="E80" s="129"/>
-      <c r="F80" s="130"/>
-      <c r="G80" s="131"/>
-      <c r="H80" s="132"/>
-      <c r="I80" s="133">
+      <c r="A80" s="81"/>
+      <c r="B80" s="10"/>
+      <c r="C80" s="95"/>
+      <c r="D80" s="97"/>
+      <c r="E80" s="83"/>
+      <c r="F80" s="104"/>
+      <c r="G80" s="34"/>
+      <c r="H80" s="102"/>
+      <c r="I80" s="149">
         <f t="shared" ref="I80:I99" si="3">SUM(F80*H80)</f>
         <v>0</v>
       </c>
-      <c r="J80" s="134"/>
-      <c r="K80" s="135"/>
+      <c r="J80" s="148"/>
+      <c r="K80" s="80"/>
     </row>
     <row r="81" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="136"/>
-      <c r="B81" s="137"/>
-      <c r="C81" s="138"/>
-      <c r="D81" s="139"/>
-      <c r="E81" s="129"/>
-      <c r="F81" s="130"/>
-      <c r="G81" s="131"/>
-      <c r="H81" s="132"/>
-      <c r="I81" s="133">
+      <c r="A81" s="81"/>
+      <c r="B81" s="82"/>
+      <c r="C81" s="95"/>
+      <c r="D81" s="97"/>
+      <c r="E81" s="83"/>
+      <c r="F81" s="104"/>
+      <c r="G81" s="34"/>
+      <c r="H81" s="102"/>
+      <c r="I81" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J81" s="134"/>
-      <c r="K81" s="135"/>
+      <c r="J81" s="148"/>
+      <c r="K81" s="80"/>
     </row>
     <row r="82" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A82" s="136"/>
-      <c r="B82" s="137"/>
-      <c r="C82" s="138"/>
-      <c r="D82" s="139"/>
-      <c r="E82" s="129"/>
-      <c r="F82" s="130"/>
-      <c r="G82" s="131"/>
-      <c r="H82" s="132"/>
-      <c r="I82" s="133">
+      <c r="A82" s="81"/>
+      <c r="B82" s="82"/>
+      <c r="C82" s="95"/>
+      <c r="D82" s="97"/>
+      <c r="E82" s="83"/>
+      <c r="F82" s="104"/>
+      <c r="G82" s="34"/>
+      <c r="H82" s="102"/>
+      <c r="I82" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J82" s="134"/>
-      <c r="K82" s="135"/>
+      <c r="J82" s="148"/>
+      <c r="K82" s="80"/>
     </row>
     <row r="83" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A83" s="136"/>
-      <c r="B83" s="137"/>
-      <c r="C83" s="138"/>
-      <c r="D83" s="139"/>
-      <c r="E83" s="141"/>
-      <c r="F83" s="130"/>
-      <c r="G83" s="131"/>
-      <c r="H83" s="132"/>
-      <c r="I83" s="133">
+      <c r="A83" s="81"/>
+      <c r="B83" s="82"/>
+      <c r="C83" s="95"/>
+      <c r="D83" s="97"/>
+      <c r="E83" s="83"/>
+      <c r="F83" s="104"/>
+      <c r="G83" s="34"/>
+      <c r="H83" s="102"/>
+      <c r="I83" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J83" s="134"/>
-      <c r="K83" s="135"/>
+      <c r="J83" s="148"/>
+      <c r="K83" s="80"/>
     </row>
     <row r="84" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A84" s="136"/>
-      <c r="B84" s="137"/>
-      <c r="C84" s="138"/>
-      <c r="D84" s="139"/>
-      <c r="E84" s="141"/>
-      <c r="F84" s="130"/>
-      <c r="G84" s="131"/>
-      <c r="H84" s="132"/>
-      <c r="I84" s="133">
+      <c r="A84" s="81"/>
+      <c r="B84" s="82"/>
+      <c r="C84" s="95"/>
+      <c r="D84" s="97"/>
+      <c r="E84" s="83"/>
+      <c r="F84" s="104"/>
+      <c r="G84" s="34"/>
+      <c r="H84" s="102"/>
+      <c r="I84" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J84" s="134"/>
-      <c r="K84" s="135"/>
+      <c r="J84" s="148"/>
+      <c r="K84" s="80"/>
     </row>
     <row r="85" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="136"/>
-      <c r="B85" s="137"/>
-      <c r="C85" s="138"/>
-      <c r="D85" s="139"/>
-      <c r="E85" s="129"/>
-      <c r="F85" s="130"/>
-      <c r="G85" s="131"/>
-      <c r="H85" s="132"/>
-      <c r="I85" s="133">
+      <c r="A85" s="81"/>
+      <c r="B85" s="82"/>
+      <c r="C85" s="95"/>
+      <c r="D85" s="97"/>
+      <c r="E85" s="83"/>
+      <c r="F85" s="104"/>
+      <c r="G85" s="34"/>
+      <c r="H85" s="102"/>
+      <c r="I85" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J85" s="134"/>
-      <c r="K85" s="135"/>
+      <c r="J85" s="148"/>
+      <c r="K85" s="80"/>
     </row>
     <row r="86" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="136"/>
-      <c r="B86" s="137"/>
-      <c r="C86" s="138"/>
-      <c r="D86" s="139"/>
-      <c r="E86" s="129"/>
-      <c r="F86" s="130"/>
-      <c r="G86" s="131"/>
-      <c r="H86" s="132"/>
-      <c r="I86" s="133">
+      <c r="A86" s="81"/>
+      <c r="B86" s="82"/>
+      <c r="C86" s="95"/>
+      <c r="D86" s="97"/>
+      <c r="E86" s="83"/>
+      <c r="F86" s="104"/>
+      <c r="G86" s="34"/>
+      <c r="H86" s="102"/>
+      <c r="I86" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J86" s="134"/>
-      <c r="K86" s="135"/>
+      <c r="J86" s="148"/>
+      <c r="K86" s="80"/>
     </row>
     <row r="87" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A87" s="136"/>
-      <c r="B87" s="137"/>
-      <c r="C87" s="138"/>
-      <c r="D87" s="139"/>
-      <c r="E87" s="129"/>
-      <c r="F87" s="130"/>
-      <c r="G87" s="131"/>
-      <c r="H87" s="132"/>
-      <c r="I87" s="133">
+      <c r="A87" s="81"/>
+      <c r="B87" s="82"/>
+      <c r="C87" s="95"/>
+      <c r="D87" s="97"/>
+      <c r="E87" s="83"/>
+      <c r="F87" s="104"/>
+      <c r="G87" s="34"/>
+      <c r="H87" s="102"/>
+      <c r="I87" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J87" s="134"/>
-      <c r="K87" s="135"/>
+      <c r="J87" s="148"/>
+      <c r="K87" s="80"/>
     </row>
     <row r="88" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="136"/>
-      <c r="B88" s="137"/>
-      <c r="C88" s="138"/>
-      <c r="D88" s="139"/>
-      <c r="E88" s="129"/>
-      <c r="F88" s="130"/>
-      <c r="G88" s="131"/>
-      <c r="H88" s="132"/>
-      <c r="I88" s="133">
+      <c r="A88" s="81"/>
+      <c r="B88" s="82"/>
+      <c r="C88" s="95"/>
+      <c r="D88" s="97"/>
+      <c r="E88" s="83"/>
+      <c r="F88" s="104"/>
+      <c r="G88" s="34"/>
+      <c r="H88" s="102"/>
+      <c r="I88" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J88" s="134"/>
-      <c r="K88" s="135"/>
+      <c r="J88" s="148"/>
+      <c r="K88" s="80"/>
     </row>
     <row r="89" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A89" s="136"/>
-      <c r="B89" s="137"/>
-      <c r="C89" s="138"/>
-      <c r="D89" s="139"/>
-      <c r="E89" s="129"/>
-      <c r="F89" s="130"/>
-      <c r="G89" s="131"/>
-      <c r="H89" s="132"/>
-      <c r="I89" s="133">
+      <c r="A89" s="81"/>
+      <c r="B89" s="82"/>
+      <c r="C89" s="95"/>
+      <c r="D89" s="97"/>
+      <c r="E89" s="83"/>
+      <c r="F89" s="104"/>
+      <c r="G89" s="34"/>
+      <c r="H89" s="102"/>
+      <c r="I89" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J89" s="134"/>
-      <c r="K89" s="135"/>
+      <c r="J89" s="148"/>
+      <c r="K89" s="80"/>
     </row>
     <row r="90" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A90" s="136"/>
-      <c r="B90" s="137"/>
-      <c r="C90" s="138"/>
-      <c r="D90" s="139"/>
-      <c r="E90" s="141"/>
-      <c r="F90" s="130"/>
-      <c r="G90" s="131"/>
-      <c r="H90" s="142"/>
-      <c r="I90" s="143">
+      <c r="A90" s="81"/>
+      <c r="B90" s="82"/>
+      <c r="C90" s="95"/>
+      <c r="D90" s="97"/>
+      <c r="E90" s="83"/>
+      <c r="F90" s="104"/>
+      <c r="G90" s="34"/>
+      <c r="H90" s="103"/>
+      <c r="I90" s="147">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J90" s="134"/>
-      <c r="K90" s="135"/>
+      <c r="J90" s="148"/>
+      <c r="K90" s="80"/>
     </row>
     <row r="91" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A91" s="136"/>
-      <c r="B91" s="137"/>
-      <c r="C91" s="138"/>
-      <c r="D91" s="139"/>
-      <c r="E91" s="141"/>
-      <c r="F91" s="130"/>
-      <c r="G91" s="131"/>
-      <c r="H91" s="144"/>
-      <c r="I91" s="143">
+      <c r="A91" s="81"/>
+      <c r="B91" s="82"/>
+      <c r="C91" s="95"/>
+      <c r="D91" s="97"/>
+      <c r="E91" s="83"/>
+      <c r="F91" s="104"/>
+      <c r="G91" s="34"/>
+      <c r="H91" s="103"/>
+      <c r="I91" s="147">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J91" s="134"/>
-      <c r="K91" s="135"/>
+      <c r="J91" s="148"/>
+      <c r="K91" s="80"/>
     </row>
     <row r="92" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A92" s="136"/>
-      <c r="B92" s="137"/>
-      <c r="C92" s="138"/>
-      <c r="D92" s="139"/>
-      <c r="E92" s="141"/>
-      <c r="F92" s="130"/>
-      <c r="G92" s="131"/>
-      <c r="H92" s="144"/>
-      <c r="I92" s="143">
+      <c r="A92" s="81"/>
+      <c r="B92" s="82"/>
+      <c r="C92" s="95"/>
+      <c r="D92" s="97"/>
+      <c r="E92" s="83"/>
+      <c r="F92" s="104"/>
+      <c r="G92" s="34"/>
+      <c r="H92" s="103"/>
+      <c r="I92" s="147">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J92" s="134"/>
-      <c r="K92" s="135"/>
+      <c r="J92" s="148"/>
+      <c r="K92" s="80"/>
     </row>
     <row r="93" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A93" s="136"/>
-      <c r="B93" s="137"/>
-      <c r="C93" s="138"/>
-      <c r="D93" s="139"/>
-      <c r="E93" s="141"/>
-      <c r="F93" s="130"/>
-      <c r="G93" s="131"/>
-      <c r="H93" s="132"/>
-      <c r="I93" s="133">
+      <c r="A93" s="81"/>
+      <c r="B93" s="82"/>
+      <c r="C93" s="95"/>
+      <c r="D93" s="97"/>
+      <c r="E93" s="83"/>
+      <c r="F93" s="104"/>
+      <c r="G93" s="34"/>
+      <c r="H93" s="102"/>
+      <c r="I93" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J93" s="134"/>
-      <c r="K93" s="135"/>
+      <c r="J93" s="148"/>
+      <c r="K93" s="80"/>
     </row>
     <row r="94" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A94" s="136"/>
-      <c r="B94" s="137"/>
-      <c r="C94" s="138"/>
-      <c r="D94" s="139"/>
-      <c r="E94" s="129"/>
-      <c r="F94" s="130"/>
-      <c r="G94" s="131"/>
-      <c r="H94" s="132"/>
-      <c r="I94" s="133">
+      <c r="A94" s="81"/>
+      <c r="B94" s="82"/>
+      <c r="C94" s="95"/>
+      <c r="D94" s="97"/>
+      <c r="E94" s="83"/>
+      <c r="F94" s="104"/>
+      <c r="G94" s="34"/>
+      <c r="H94" s="102"/>
+      <c r="I94" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J94" s="134"/>
-      <c r="K94" s="135"/>
+      <c r="J94" s="148"/>
+      <c r="K94" s="80"/>
     </row>
     <row r="95" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A95" s="136"/>
-      <c r="B95" s="137"/>
-      <c r="C95" s="138"/>
-      <c r="D95" s="139"/>
-      <c r="E95" s="129"/>
-      <c r="F95" s="130"/>
-      <c r="G95" s="131"/>
-      <c r="H95" s="132"/>
-      <c r="I95" s="133">
+      <c r="A95" s="81"/>
+      <c r="B95" s="82"/>
+      <c r="C95" s="95"/>
+      <c r="D95" s="97"/>
+      <c r="E95" s="83"/>
+      <c r="F95" s="104"/>
+      <c r="G95" s="34"/>
+      <c r="H95" s="102"/>
+      <c r="I95" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J95" s="134"/>
-      <c r="K95" s="135"/>
+      <c r="J95" s="148"/>
+      <c r="K95" s="80"/>
     </row>
     <row r="96" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A96" s="136"/>
-      <c r="B96" s="137"/>
-      <c r="C96" s="138"/>
-      <c r="D96" s="139"/>
-      <c r="E96" s="129"/>
-      <c r="F96" s="130"/>
-      <c r="G96" s="131"/>
-      <c r="H96" s="132"/>
-      <c r="I96" s="133">
+      <c r="A96" s="81"/>
+      <c r="B96" s="82"/>
+      <c r="C96" s="95"/>
+      <c r="D96" s="97"/>
+      <c r="E96" s="83"/>
+      <c r="F96" s="104"/>
+      <c r="G96" s="34"/>
+      <c r="H96" s="102"/>
+      <c r="I96" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J96" s="134"/>
-      <c r="K96" s="135"/>
+      <c r="J96" s="148"/>
+      <c r="K96" s="80"/>
     </row>
     <row r="97" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A97" s="136"/>
-      <c r="B97" s="137"/>
-      <c r="C97" s="138"/>
-      <c r="D97" s="139"/>
-      <c r="E97" s="129"/>
-      <c r="F97" s="130"/>
-      <c r="G97" s="131"/>
-      <c r="H97" s="132"/>
-      <c r="I97" s="133">
+      <c r="A97" s="81"/>
+      <c r="B97" s="82"/>
+      <c r="C97" s="95"/>
+      <c r="D97" s="97"/>
+      <c r="E97" s="83"/>
+      <c r="F97" s="104"/>
+      <c r="G97" s="34"/>
+      <c r="H97" s="102"/>
+      <c r="I97" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J97" s="134"/>
-      <c r="K97" s="135"/>
+      <c r="J97" s="148"/>
+      <c r="K97" s="80"/>
     </row>
     <row r="98" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A98" s="136"/>
-      <c r="B98" s="137"/>
-      <c r="C98" s="138"/>
-      <c r="D98" s="139"/>
-      <c r="E98" s="145"/>
-      <c r="F98" s="130"/>
-      <c r="G98" s="131"/>
-      <c r="H98" s="132"/>
-      <c r="I98" s="133">
+      <c r="A98" s="81"/>
+      <c r="B98" s="82"/>
+      <c r="C98" s="95"/>
+      <c r="D98" s="97"/>
+      <c r="E98" s="98"/>
+      <c r="F98" s="104"/>
+      <c r="G98" s="34"/>
+      <c r="H98" s="102"/>
+      <c r="I98" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J98" s="134"/>
-      <c r="K98" s="135"/>
+      <c r="J98" s="148"/>
+      <c r="K98" s="80"/>
     </row>
     <row r="99" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A99" s="136"/>
-      <c r="B99" s="137"/>
-      <c r="C99" s="138"/>
-      <c r="D99" s="139"/>
-      <c r="E99" s="129"/>
-      <c r="F99" s="130"/>
-      <c r="G99" s="131"/>
-      <c r="H99" s="132"/>
-      <c r="I99" s="133">
+      <c r="A99" s="81"/>
+      <c r="B99" s="82"/>
+      <c r="C99" s="95"/>
+      <c r="D99" s="97"/>
+      <c r="E99" s="83"/>
+      <c r="F99" s="104"/>
+      <c r="G99" s="34"/>
+      <c r="H99" s="102"/>
+      <c r="I99" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J99" s="134"/>
-      <c r="K99" s="135"/>
+      <c r="J99" s="148"/>
+      <c r="K99" s="80"/>
     </row>
     <row r="100" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A100" s="146"/>
-      <c r="B100" s="147"/>
-      <c r="C100" s="148" t="s">
-        <v>18</v>
-      </c>
-      <c r="D100" s="149"/>
-      <c r="E100" s="150"/>
-      <c r="F100" s="150"/>
-      <c r="G100" s="151"/>
-      <c r="H100" s="132"/>
-      <c r="I100" s="133">
+      <c r="A100" s="101"/>
+      <c r="B100" s="84"/>
+      <c r="C100" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="D100" s="84"/>
+      <c r="E100" s="99"/>
+      <c r="F100" s="105"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="102"/>
+      <c r="I100" s="149">
         <f>SUM(I77:J99)</f>
         <v>0</v>
       </c>
-      <c r="J100" s="134"/>
-      <c r="K100" s="152"/>
+      <c r="J100" s="148"/>
+      <c r="K100" s="85"/>
     </row>
     <row r="101" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="114" t="s">
-        <v>16</v>
-      </c>
-      <c r="B101" s="114"/>
-      <c r="C101" s="115">
+      <c r="A101" s="141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" s="141"/>
+      <c r="C101" s="142">
         <f>表紙!C115</f>
         <v>0</v>
       </c>
-      <c r="D101" s="115"/>
-      <c r="E101" s="115"/>
-      <c r="F101" s="116" t="s">
-        <v>17</v>
-      </c>
-      <c r="G101" s="116"/>
-      <c r="H101" s="116"/>
-      <c r="I101" s="116"/>
-      <c r="J101" s="114" t="s">
-        <v>86</v>
-      </c>
-      <c r="K101" s="114"/>
+      <c r="D101" s="142"/>
+      <c r="E101" s="142"/>
+      <c r="F101" s="143" t="s">
+        <v>16</v>
+      </c>
+      <c r="G101" s="143"/>
+      <c r="H101" s="143"/>
+      <c r="I101" s="143"/>
+      <c r="J101" s="144" t="s">
+        <v>85</v>
+      </c>
+      <c r="K101" s="144"/>
     </row>
     <row r="102" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="117"/>
-      <c r="B102" s="118" t="s">
+      <c r="A102" s="73"/>
+      <c r="B102" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C102" s="119"/>
-      <c r="D102" s="120" t="s">
+      <c r="C102" s="75"/>
+      <c r="D102" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="E102" s="121"/>
-      <c r="F102" s="122" t="s">
-        <v>82</v>
-      </c>
-      <c r="G102" s="122" t="s">
+      <c r="E102" s="77"/>
+      <c r="F102" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="G102" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="H102" s="122" t="s">
+      <c r="H102" s="78" t="s">
+        <v>88</v>
+      </c>
+      <c r="I102" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="I102" s="123" t="s">
+      <c r="J102" s="146"/>
+      <c r="K102" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="J102" s="124"/>
-      <c r="K102" s="122" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="103" spans="1:11" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A103" s="125"/>
-      <c r="B103" s="126"/>
-      <c r="C103" s="127"/>
-      <c r="D103" s="128"/>
-      <c r="E103" s="129"/>
-      <c r="F103" s="130"/>
-      <c r="G103" s="131"/>
-      <c r="H103" s="132"/>
-      <c r="I103" s="133">
+      <c r="A103" s="100"/>
+      <c r="B103" s="93"/>
+      <c r="C103" s="94"/>
+      <c r="D103" s="96"/>
+      <c r="E103" s="83"/>
+      <c r="F103" s="104"/>
+      <c r="G103" s="34"/>
+      <c r="H103" s="102"/>
+      <c r="I103" s="149">
         <f>SUM(F103*H103)</f>
         <v>0</v>
       </c>
-      <c r="J103" s="134"/>
-      <c r="K103" s="135"/>
+      <c r="J103" s="148"/>
+      <c r="K103" s="80"/>
     </row>
     <row r="104" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A104" s="136"/>
-      <c r="B104" s="137"/>
-      <c r="C104" s="138"/>
-      <c r="D104" s="139"/>
-      <c r="E104" s="129"/>
-      <c r="F104" s="130"/>
-      <c r="G104" s="131"/>
-      <c r="H104" s="132"/>
-      <c r="I104" s="133">
+      <c r="A104" s="81"/>
+      <c r="B104" s="82"/>
+      <c r="C104" s="95"/>
+      <c r="D104" s="97"/>
+      <c r="E104" s="83"/>
+      <c r="F104" s="104"/>
+      <c r="G104" s="34"/>
+      <c r="H104" s="102"/>
+      <c r="I104" s="149">
         <f>SUM(F104*H104)</f>
         <v>0</v>
       </c>
-      <c r="J104" s="134"/>
-      <c r="K104" s="135"/>
+      <c r="J104" s="148"/>
+      <c r="K104" s="80"/>
     </row>
     <row r="105" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A105" s="136"/>
-      <c r="B105" s="140"/>
-      <c r="C105" s="138"/>
-      <c r="D105" s="139"/>
-      <c r="E105" s="129"/>
-      <c r="F105" s="130"/>
-      <c r="G105" s="131"/>
-      <c r="H105" s="132"/>
-      <c r="I105" s="133">
+      <c r="A105" s="81"/>
+      <c r="B105" s="10"/>
+      <c r="C105" s="95"/>
+      <c r="D105" s="97"/>
+      <c r="E105" s="83"/>
+      <c r="F105" s="104"/>
+      <c r="G105" s="34"/>
+      <c r="H105" s="102"/>
+      <c r="I105" s="149">
         <f t="shared" ref="I105:I124" si="4">SUM(F105*H105)</f>
         <v>0</v>
       </c>
-      <c r="J105" s="134"/>
-      <c r="K105" s="135"/>
+      <c r="J105" s="148"/>
+      <c r="K105" s="80"/>
     </row>
     <row r="106" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A106" s="136"/>
-      <c r="B106" s="137"/>
-      <c r="C106" s="138"/>
-      <c r="D106" s="139"/>
-      <c r="E106" s="129"/>
-      <c r="F106" s="130"/>
-      <c r="G106" s="131"/>
-      <c r="H106" s="132"/>
-      <c r="I106" s="133">
+      <c r="A106" s="81"/>
+      <c r="B106" s="82"/>
+      <c r="C106" s="95"/>
+      <c r="D106" s="97"/>
+      <c r="E106" s="83"/>
+      <c r="F106" s="104"/>
+      <c r="G106" s="34"/>
+      <c r="H106" s="102"/>
+      <c r="I106" s="149">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J106" s="134"/>
-      <c r="K106" s="135"/>
+      <c r="J106" s="148"/>
+      <c r="K106" s="80"/>
     </row>
     <row r="107" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A107" s="136"/>
-      <c r="B107" s="137"/>
-      <c r="C107" s="138"/>
-      <c r="D107" s="139"/>
-      <c r="E107" s="129"/>
-      <c r="F107" s="130"/>
-      <c r="G107" s="131"/>
-      <c r="H107" s="132"/>
-      <c r="I107" s="133">
+      <c r="A107" s="81"/>
+      <c r="B107" s="82"/>
+      <c r="C107" s="95"/>
+      <c r="D107" s="97"/>
+      <c r="E107" s="83"/>
+      <c r="F107" s="104"/>
+      <c r="G107" s="34"/>
+      <c r="H107" s="102"/>
+      <c r="I107" s="149">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J107" s="134"/>
-      <c r="K107" s="135"/>
+      <c r="J107" s="148"/>
+      <c r="K107" s="80"/>
     </row>
     <row r="108" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A108" s="136"/>
-      <c r="B108" s="137"/>
-      <c r="C108" s="138"/>
-      <c r="D108" s="139"/>
-      <c r="E108" s="141"/>
-      <c r="F108" s="130"/>
-      <c r="G108" s="131"/>
-      <c r="H108" s="132"/>
-      <c r="I108" s="133">
+      <c r="A108" s="81"/>
+      <c r="B108" s="82"/>
+      <c r="C108" s="95"/>
+      <c r="D108" s="97"/>
+      <c r="E108" s="83"/>
+      <c r="F108" s="104"/>
+      <c r="G108" s="34"/>
+      <c r="H108" s="102"/>
+      <c r="I108" s="149">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J108" s="134"/>
-      <c r="K108" s="135"/>
+      <c r="J108" s="148"/>
+      <c r="K108" s="80"/>
     </row>
     <row r="109" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A109" s="136"/>
-      <c r="B109" s="137"/>
-      <c r="C109" s="138"/>
-      <c r="D109" s="139"/>
-      <c r="E109" s="141"/>
-      <c r="F109" s="130"/>
-      <c r="G109" s="131"/>
-      <c r="H109" s="132"/>
-      <c r="I109" s="133">
+      <c r="A109" s="81"/>
+      <c r="B109" s="82"/>
+      <c r="C109" s="95"/>
+      <c r="D109" s="97"/>
+      <c r="E109" s="83"/>
+      <c r="F109" s="104"/>
+      <c r="G109" s="34"/>
+      <c r="H109" s="102"/>
+      <c r="I109" s="149">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J109" s="134"/>
-      <c r="K109" s="135"/>
+      <c r="J109" s="148"/>
+      <c r="K109" s="80"/>
     </row>
     <row r="110" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A110" s="136"/>
-      <c r="B110" s="137"/>
-      <c r="C110" s="138"/>
-      <c r="D110" s="139"/>
-      <c r="E110" s="129"/>
-      <c r="F110" s="130"/>
-      <c r="G110" s="131"/>
-      <c r="H110" s="132"/>
-      <c r="I110" s="133">
+      <c r="A110" s="81"/>
+      <c r="B110" s="82"/>
+      <c r="C110" s="95"/>
+      <c r="D110" s="97"/>
+      <c r="E110" s="83"/>
+      <c r="F110" s="104"/>
+      <c r="G110" s="34"/>
+      <c r="H110" s="102"/>
+      <c r="I110" s="149">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J110" s="134"/>
-      <c r="K110" s="135"/>
+      <c r="J110" s="148"/>
+      <c r="K110" s="80"/>
     </row>
     <row r="111" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A111" s="136"/>
-      <c r="B111" s="137"/>
-      <c r="C111" s="138"/>
-      <c r="D111" s="139"/>
-      <c r="E111" s="129"/>
-      <c r="F111" s="130"/>
-      <c r="G111" s="131"/>
-      <c r="H111" s="132"/>
-      <c r="I111" s="133">
+      <c r="A111" s="81"/>
+      <c r="B111" s="82"/>
+      <c r="C111" s="95"/>
+      <c r="D111" s="97"/>
+      <c r="E111" s="83"/>
+      <c r="F111" s="104"/>
+      <c r="G111" s="34"/>
+      <c r="H111" s="102"/>
+      <c r="I111" s="149">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J111" s="134"/>
-      <c r="K111" s="135"/>
+      <c r="J111" s="148"/>
+      <c r="K111" s="80"/>
     </row>
     <row r="112" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A112" s="136"/>
-      <c r="B112" s="137"/>
-      <c r="C112" s="138"/>
-      <c r="D112" s="139"/>
-      <c r="E112" s="129"/>
-      <c r="F112" s="130"/>
-      <c r="G112" s="131"/>
-      <c r="H112" s="132"/>
-      <c r="I112" s="133">
+      <c r="A112" s="81"/>
+      <c r="B112" s="82"/>
+      <c r="C112" s="95"/>
+      <c r="D112" s="97"/>
+      <c r="E112" s="83"/>
+      <c r="F112" s="104"/>
+      <c r="G112" s="34"/>
+      <c r="H112" s="102"/>
+      <c r="I112" s="149">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J112" s="134"/>
-      <c r="K112" s="135"/>
+      <c r="J112" s="148"/>
+      <c r="K112" s="80"/>
     </row>
     <row r="113" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A113" s="136"/>
-      <c r="B113" s="137"/>
-      <c r="C113" s="138"/>
-      <c r="D113" s="139"/>
-      <c r="E113" s="129"/>
-      <c r="F113" s="130"/>
-      <c r="G113" s="131"/>
-      <c r="H113" s="132"/>
-      <c r="I113" s="133">
+      <c r="A113" s="81"/>
+      <c r="B113" s="82"/>
+      <c r="C113" s="95"/>
+      <c r="D113" s="97"/>
+      <c r="E113" s="83"/>
+      <c r="F113" s="104"/>
+      <c r="G113" s="34"/>
+      <c r="H113" s="102"/>
+      <c r="I113" s="149">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J113" s="134"/>
-      <c r="K113" s="135"/>
+      <c r="J113" s="148"/>
+      <c r="K113" s="80"/>
     </row>
     <row r="114" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A114" s="136"/>
-      <c r="B114" s="137"/>
-      <c r="C114" s="138"/>
-      <c r="D114" s="139"/>
-      <c r="E114" s="129"/>
-      <c r="F114" s="130"/>
-      <c r="G114" s="131"/>
-      <c r="H114" s="132"/>
-      <c r="I114" s="133">
+      <c r="A114" s="81"/>
+      <c r="B114" s="82"/>
+      <c r="C114" s="95"/>
+      <c r="D114" s="97"/>
+      <c r="E114" s="83"/>
+      <c r="F114" s="104"/>
+      <c r="G114" s="34"/>
+      <c r="H114" s="102"/>
+      <c r="I114" s="149">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J114" s="134"/>
-      <c r="K114" s="135"/>
+      <c r="J114" s="148"/>
+      <c r="K114" s="80"/>
     </row>
     <row r="115" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A115" s="136"/>
-      <c r="B115" s="137"/>
-      <c r="C115" s="138"/>
-      <c r="D115" s="139"/>
-      <c r="E115" s="141"/>
-      <c r="F115" s="130"/>
-      <c r="G115" s="131"/>
-      <c r="H115" s="142"/>
-      <c r="I115" s="143">
+      <c r="A115" s="81"/>
+      <c r="B115" s="82"/>
+      <c r="C115" s="95"/>
+      <c r="D115" s="97"/>
+      <c r="E115" s="83"/>
+      <c r="F115" s="104"/>
+      <c r="G115" s="34"/>
+      <c r="H115" s="103"/>
+      <c r="I115" s="147">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J115" s="134"/>
-      <c r="K115" s="135"/>
+      <c r="J115" s="148"/>
+      <c r="K115" s="80"/>
     </row>
     <row r="116" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A116" s="136"/>
-      <c r="B116" s="137"/>
-      <c r="C116" s="138"/>
-      <c r="D116" s="139"/>
-      <c r="E116" s="141"/>
-      <c r="F116" s="130"/>
-      <c r="G116" s="131"/>
-      <c r="H116" s="144"/>
-      <c r="I116" s="143">
+      <c r="A116" s="81"/>
+      <c r="B116" s="82"/>
+      <c r="C116" s="95"/>
+      <c r="D116" s="97"/>
+      <c r="E116" s="83"/>
+      <c r="F116" s="104"/>
+      <c r="G116" s="34"/>
+      <c r="H116" s="103"/>
+      <c r="I116" s="147">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J116" s="134"/>
-      <c r="K116" s="135"/>
+      <c r="J116" s="148"/>
+      <c r="K116" s="80"/>
     </row>
     <row r="117" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A117" s="136"/>
-      <c r="B117" s="137"/>
-      <c r="C117" s="138"/>
-      <c r="D117" s="139"/>
-      <c r="E117" s="141"/>
-      <c r="F117" s="130"/>
-      <c r="G117" s="131"/>
-      <c r="H117" s="144"/>
-      <c r="I117" s="143">
+      <c r="A117" s="81"/>
+      <c r="B117" s="82"/>
+      <c r="C117" s="95"/>
+      <c r="D117" s="97"/>
+      <c r="E117" s="83"/>
+      <c r="F117" s="104"/>
+      <c r="G117" s="34"/>
+      <c r="H117" s="103"/>
+      <c r="I117" s="147">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J117" s="134"/>
-      <c r="K117" s="135"/>
+      <c r="J117" s="148"/>
+      <c r="K117" s="80"/>
     </row>
     <row r="118" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A118" s="136"/>
-      <c r="B118" s="137"/>
-      <c r="C118" s="138"/>
-      <c r="D118" s="139"/>
-      <c r="E118" s="141"/>
-      <c r="F118" s="130"/>
-      <c r="G118" s="131"/>
-      <c r="H118" s="132"/>
-      <c r="I118" s="133">
+      <c r="A118" s="81"/>
+      <c r="B118" s="82"/>
+      <c r="C118" s="95"/>
+      <c r="D118" s="97"/>
+      <c r="E118" s="83"/>
+      <c r="F118" s="104"/>
+      <c r="G118" s="34"/>
+      <c r="H118" s="102"/>
+      <c r="I118" s="149">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J118" s="134"/>
-      <c r="K118" s="135"/>
+      <c r="J118" s="148"/>
+      <c r="K118" s="80"/>
     </row>
     <row r="119" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A119" s="136"/>
-      <c r="B119" s="137"/>
-      <c r="C119" s="138"/>
-      <c r="D119" s="139"/>
-      <c r="E119" s="129"/>
-      <c r="F119" s="130"/>
-      <c r="G119" s="131"/>
-      <c r="H119" s="132"/>
-      <c r="I119" s="133">
+      <c r="A119" s="81"/>
+      <c r="B119" s="82"/>
+      <c r="C119" s="95"/>
+      <c r="D119" s="97"/>
+      <c r="E119" s="83"/>
+      <c r="F119" s="104"/>
+      <c r="G119" s="34"/>
+      <c r="H119" s="102"/>
+      <c r="I119" s="149">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J119" s="134"/>
-      <c r="K119" s="135"/>
+      <c r="J119" s="148"/>
+      <c r="K119" s="80"/>
     </row>
     <row r="120" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A120" s="136"/>
-      <c r="B120" s="137"/>
-      <c r="C120" s="138"/>
-      <c r="D120" s="139"/>
-      <c r="E120" s="129"/>
-      <c r="F120" s="130"/>
-      <c r="G120" s="131"/>
-      <c r="H120" s="132"/>
-      <c r="I120" s="133">
+      <c r="A120" s="81"/>
+      <c r="B120" s="82"/>
+      <c r="C120" s="95"/>
+      <c r="D120" s="97"/>
+      <c r="E120" s="83"/>
+      <c r="F120" s="104"/>
+      <c r="G120" s="34"/>
+      <c r="H120" s="102"/>
+      <c r="I120" s="149">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J120" s="134"/>
-      <c r="K120" s="135"/>
+      <c r="J120" s="148"/>
+      <c r="K120" s="80"/>
     </row>
     <row r="121" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A121" s="136"/>
-      <c r="B121" s="137"/>
-      <c r="C121" s="138"/>
-      <c r="D121" s="139"/>
-      <c r="E121" s="129"/>
-      <c r="F121" s="130"/>
-      <c r="G121" s="131"/>
-      <c r="H121" s="132"/>
-      <c r="I121" s="133">
+      <c r="A121" s="81"/>
+      <c r="B121" s="82"/>
+      <c r="C121" s="95"/>
+      <c r="D121" s="97"/>
+      <c r="E121" s="83"/>
+      <c r="F121" s="104"/>
+      <c r="G121" s="34"/>
+      <c r="H121" s="102"/>
+      <c r="I121" s="149">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J121" s="134"/>
-      <c r="K121" s="135"/>
+      <c r="J121" s="148"/>
+      <c r="K121" s="80"/>
     </row>
     <row r="122" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A122" s="136"/>
-      <c r="B122" s="137"/>
-      <c r="C122" s="138"/>
-      <c r="D122" s="139"/>
-      <c r="E122" s="129"/>
-      <c r="F122" s="130"/>
-      <c r="G122" s="131"/>
-      <c r="H122" s="132"/>
-      <c r="I122" s="133">
+      <c r="A122" s="81"/>
+      <c r="B122" s="82"/>
+      <c r="C122" s="95"/>
+      <c r="D122" s="97"/>
+      <c r="E122" s="83"/>
+      <c r="F122" s="104"/>
+      <c r="G122" s="34"/>
+      <c r="H122" s="102"/>
+      <c r="I122" s="149">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J122" s="134"/>
-      <c r="K122" s="135"/>
+      <c r="J122" s="148"/>
+      <c r="K122" s="80"/>
     </row>
     <row r="123" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A123" s="136"/>
-      <c r="B123" s="137"/>
-      <c r="C123" s="138"/>
-      <c r="D123" s="139"/>
-      <c r="E123" s="145"/>
-      <c r="F123" s="130"/>
-      <c r="G123" s="131"/>
-      <c r="H123" s="132"/>
-      <c r="I123" s="133">
+      <c r="A123" s="81"/>
+      <c r="B123" s="82"/>
+      <c r="C123" s="95"/>
+      <c r="D123" s="97"/>
+      <c r="E123" s="98"/>
+      <c r="F123" s="104"/>
+      <c r="G123" s="34"/>
+      <c r="H123" s="102"/>
+      <c r="I123" s="149">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J123" s="134"/>
-      <c r="K123" s="135"/>
+      <c r="J123" s="148"/>
+      <c r="K123" s="80"/>
     </row>
     <row r="124" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A124" s="136"/>
-      <c r="B124" s="137"/>
-      <c r="C124" s="138"/>
-      <c r="D124" s="139"/>
-      <c r="E124" s="129"/>
-      <c r="F124" s="130"/>
-      <c r="G124" s="131"/>
-      <c r="H124" s="132"/>
-      <c r="I124" s="133">
+      <c r="A124" s="81"/>
+      <c r="B124" s="82"/>
+      <c r="C124" s="95"/>
+      <c r="D124" s="97"/>
+      <c r="E124" s="83"/>
+      <c r="F124" s="104"/>
+      <c r="G124" s="34"/>
+      <c r="H124" s="102"/>
+      <c r="I124" s="149">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J124" s="134"/>
-      <c r="K124" s="135"/>
+      <c r="J124" s="148"/>
+      <c r="K124" s="80"/>
     </row>
     <row r="125" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A125" s="146"/>
-      <c r="B125" s="147"/>
-      <c r="C125" s="148" t="s">
-        <v>18</v>
-      </c>
-      <c r="D125" s="149"/>
-      <c r="E125" s="150"/>
-      <c r="F125" s="150"/>
-      <c r="G125" s="151"/>
-      <c r="H125" s="132"/>
-      <c r="I125" s="133">
+      <c r="A125" s="101"/>
+      <c r="B125" s="84"/>
+      <c r="C125" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="D125" s="84"/>
+      <c r="E125" s="99"/>
+      <c r="F125" s="105"/>
+      <c r="G125" s="6"/>
+      <c r="H125" s="102"/>
+      <c r="I125" s="149">
         <f>SUM(I102:J124)</f>
         <v>0</v>
       </c>
-      <c r="J125" s="134"/>
-      <c r="K125" s="152"/>
+      <c r="J125" s="148"/>
+      <c r="K125" s="85"/>
     </row>
     <row r="126" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="114" t="s">
-        <v>16</v>
-      </c>
-      <c r="B126" s="114"/>
-      <c r="C126" s="115">
+      <c r="A126" s="141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" s="141"/>
+      <c r="C126" s="142">
         <f>表紙!C140</f>
         <v>0</v>
       </c>
-      <c r="D126" s="115"/>
-      <c r="E126" s="115"/>
-      <c r="F126" s="116" t="s">
-        <v>17</v>
-      </c>
-      <c r="G126" s="116"/>
-      <c r="H126" s="116"/>
-      <c r="I126" s="116"/>
-      <c r="J126" s="114" t="s">
-        <v>87</v>
-      </c>
-      <c r="K126" s="114"/>
+      <c r="D126" s="142"/>
+      <c r="E126" s="142"/>
+      <c r="F126" s="143" t="s">
+        <v>16</v>
+      </c>
+      <c r="G126" s="143"/>
+      <c r="H126" s="143"/>
+      <c r="I126" s="143"/>
+      <c r="J126" s="144" t="s">
+        <v>86</v>
+      </c>
+      <c r="K126" s="144"/>
     </row>
     <row r="127" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="117"/>
-      <c r="B127" s="118" t="s">
+      <c r="A127" s="73"/>
+      <c r="B127" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C127" s="119"/>
-      <c r="D127" s="120" t="s">
+      <c r="C127" s="75"/>
+      <c r="D127" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="E127" s="121"/>
-      <c r="F127" s="122" t="s">
-        <v>82</v>
-      </c>
-      <c r="G127" s="122" t="s">
+      <c r="E127" s="77"/>
+      <c r="F127" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="G127" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="H127" s="122" t="s">
+      <c r="H127" s="78" t="s">
+        <v>88</v>
+      </c>
+      <c r="I127" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="I127" s="123" t="s">
+      <c r="J127" s="146"/>
+      <c r="K127" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="J127" s="124"/>
-      <c r="K127" s="122" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="128" spans="1:11" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A128" s="125"/>
-      <c r="B128" s="126"/>
-      <c r="C128" s="127"/>
-      <c r="D128" s="128"/>
-      <c r="E128" s="129"/>
-      <c r="F128" s="130"/>
-      <c r="G128" s="131"/>
-      <c r="H128" s="132"/>
-      <c r="I128" s="133">
+      <c r="A128" s="100"/>
+      <c r="B128" s="93"/>
+      <c r="C128" s="94"/>
+      <c r="D128" s="96"/>
+      <c r="E128" s="83"/>
+      <c r="F128" s="104"/>
+      <c r="G128" s="34"/>
+      <c r="H128" s="102"/>
+      <c r="I128" s="149">
         <f>SUM(F128*H128)</f>
         <v>0</v>
       </c>
-      <c r="J128" s="134"/>
-      <c r="K128" s="135"/>
+      <c r="J128" s="148"/>
+      <c r="K128" s="80"/>
     </row>
     <row r="129" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A129" s="136"/>
-      <c r="B129" s="137"/>
-      <c r="C129" s="138"/>
-      <c r="D129" s="139"/>
-      <c r="E129" s="129"/>
-      <c r="F129" s="130"/>
-      <c r="G129" s="131"/>
-      <c r="H129" s="132"/>
-      <c r="I129" s="133">
+      <c r="A129" s="81"/>
+      <c r="B129" s="82"/>
+      <c r="C129" s="95"/>
+      <c r="D129" s="97"/>
+      <c r="E129" s="83"/>
+      <c r="F129" s="104"/>
+      <c r="G129" s="34"/>
+      <c r="H129" s="102"/>
+      <c r="I129" s="149">
         <f>SUM(F129*H129)</f>
         <v>0</v>
       </c>
-      <c r="J129" s="134"/>
-      <c r="K129" s="135"/>
+      <c r="J129" s="148"/>
+      <c r="K129" s="80"/>
     </row>
     <row r="130" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A130" s="136"/>
-      <c r="B130" s="140"/>
-      <c r="C130" s="138"/>
-      <c r="D130" s="139"/>
-      <c r="E130" s="129"/>
-      <c r="F130" s="130"/>
-      <c r="G130" s="131"/>
-      <c r="H130" s="132"/>
-      <c r="I130" s="133">
+      <c r="A130" s="81"/>
+      <c r="B130" s="10"/>
+      <c r="C130" s="95"/>
+      <c r="D130" s="97"/>
+      <c r="E130" s="83"/>
+      <c r="F130" s="104"/>
+      <c r="G130" s="34"/>
+      <c r="H130" s="102"/>
+      <c r="I130" s="149">
         <f t="shared" ref="I130:I149" si="5">SUM(F130*H130)</f>
         <v>0</v>
       </c>
-      <c r="J130" s="134"/>
-      <c r="K130" s="135"/>
+      <c r="J130" s="148"/>
+      <c r="K130" s="80"/>
     </row>
     <row r="131" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A131" s="136"/>
-      <c r="B131" s="137"/>
-      <c r="C131" s="138"/>
-      <c r="D131" s="139"/>
-      <c r="E131" s="129"/>
-      <c r="F131" s="130"/>
-      <c r="G131" s="131"/>
-      <c r="H131" s="132"/>
-      <c r="I131" s="133">
+      <c r="A131" s="81"/>
+      <c r="B131" s="82"/>
+      <c r="C131" s="95"/>
+      <c r="D131" s="97"/>
+      <c r="E131" s="83"/>
+      <c r="F131" s="104"/>
+      <c r="G131" s="34"/>
+      <c r="H131" s="102"/>
+      <c r="I131" s="149">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J131" s="134"/>
-      <c r="K131" s="135"/>
+      <c r="J131" s="148"/>
+      <c r="K131" s="80"/>
     </row>
     <row r="132" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A132" s="136"/>
-      <c r="B132" s="137"/>
-      <c r="C132" s="138"/>
-      <c r="D132" s="139"/>
-      <c r="E132" s="129"/>
-      <c r="F132" s="130"/>
-      <c r="G132" s="131"/>
-      <c r="H132" s="132"/>
-      <c r="I132" s="133">
+      <c r="A132" s="81"/>
+      <c r="B132" s="82"/>
+      <c r="C132" s="95"/>
+      <c r="D132" s="97"/>
+      <c r="E132" s="83"/>
+      <c r="F132" s="104"/>
+      <c r="G132" s="34"/>
+      <c r="H132" s="102"/>
+      <c r="I132" s="149">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J132" s="134"/>
-      <c r="K132" s="135"/>
+      <c r="J132" s="148"/>
+      <c r="K132" s="80"/>
     </row>
     <row r="133" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A133" s="136"/>
-      <c r="B133" s="137"/>
-      <c r="C133" s="138"/>
-      <c r="D133" s="139"/>
-      <c r="E133" s="141"/>
-      <c r="F133" s="130"/>
-      <c r="G133" s="131"/>
-      <c r="H133" s="132"/>
-      <c r="I133" s="133">
+      <c r="A133" s="81"/>
+      <c r="B133" s="82"/>
+      <c r="C133" s="95"/>
+      <c r="D133" s="97"/>
+      <c r="E133" s="83"/>
+      <c r="F133" s="104"/>
+      <c r="G133" s="34"/>
+      <c r="H133" s="102"/>
+      <c r="I133" s="149">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J133" s="134"/>
-      <c r="K133" s="135"/>
+      <c r="J133" s="148"/>
+      <c r="K133" s="80"/>
     </row>
     <row r="134" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A134" s="136"/>
-      <c r="B134" s="137"/>
-      <c r="C134" s="138"/>
-      <c r="D134" s="139"/>
-      <c r="E134" s="141"/>
-      <c r="F134" s="130"/>
-      <c r="G134" s="131"/>
-      <c r="H134" s="132"/>
-      <c r="I134" s="133">
+      <c r="A134" s="81"/>
+      <c r="B134" s="82"/>
+      <c r="C134" s="95"/>
+      <c r="D134" s="97"/>
+      <c r="E134" s="83"/>
+      <c r="F134" s="104"/>
+      <c r="G134" s="34"/>
+      <c r="H134" s="102"/>
+      <c r="I134" s="149">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J134" s="134"/>
-      <c r="K134" s="135"/>
+      <c r="J134" s="148"/>
+      <c r="K134" s="80"/>
     </row>
     <row r="135" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A135" s="136"/>
-      <c r="B135" s="137"/>
-      <c r="C135" s="138"/>
-      <c r="D135" s="139"/>
-      <c r="E135" s="129"/>
-      <c r="F135" s="130"/>
-      <c r="G135" s="131"/>
-      <c r="H135" s="132"/>
-      <c r="I135" s="133">
+      <c r="A135" s="81"/>
+      <c r="B135" s="82"/>
+      <c r="C135" s="95"/>
+      <c r="D135" s="97"/>
+      <c r="E135" s="83"/>
+      <c r="F135" s="104"/>
+      <c r="G135" s="34"/>
+      <c r="H135" s="102"/>
+      <c r="I135" s="149">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J135" s="134"/>
-      <c r="K135" s="135"/>
+      <c r="J135" s="148"/>
+      <c r="K135" s="80"/>
     </row>
     <row r="136" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A136" s="136"/>
-      <c r="B136" s="137"/>
-      <c r="C136" s="138"/>
-      <c r="D136" s="139"/>
-      <c r="E136" s="129"/>
-      <c r="F136" s="130"/>
-      <c r="G136" s="131"/>
-      <c r="H136" s="132"/>
-      <c r="I136" s="133">
+      <c r="A136" s="81"/>
+      <c r="B136" s="82"/>
+      <c r="C136" s="95"/>
+      <c r="D136" s="97"/>
+      <c r="E136" s="83"/>
+      <c r="F136" s="104"/>
+      <c r="G136" s="34"/>
+      <c r="H136" s="102"/>
+      <c r="I136" s="149">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J136" s="134"/>
-      <c r="K136" s="135"/>
+      <c r="J136" s="148"/>
+      <c r="K136" s="80"/>
     </row>
     <row r="137" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A137" s="136"/>
-      <c r="B137" s="137"/>
-      <c r="C137" s="138"/>
-      <c r="D137" s="139"/>
-      <c r="E137" s="129"/>
-      <c r="F137" s="130"/>
-      <c r="G137" s="131"/>
-      <c r="H137" s="132"/>
-      <c r="I137" s="133">
+      <c r="A137" s="81"/>
+      <c r="B137" s="82"/>
+      <c r="C137" s="95"/>
+      <c r="D137" s="97"/>
+      <c r="E137" s="83"/>
+      <c r="F137" s="104"/>
+      <c r="G137" s="34"/>
+      <c r="H137" s="102"/>
+      <c r="I137" s="149">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J137" s="134"/>
-      <c r="K137" s="135"/>
+      <c r="J137" s="148"/>
+      <c r="K137" s="80"/>
     </row>
     <row r="138" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A138" s="136"/>
-      <c r="B138" s="137"/>
-      <c r="C138" s="138"/>
-      <c r="D138" s="139"/>
-      <c r="E138" s="129"/>
-      <c r="F138" s="130"/>
-      <c r="G138" s="131"/>
-      <c r="H138" s="132"/>
-      <c r="I138" s="133">
+      <c r="A138" s="81"/>
+      <c r="B138" s="82"/>
+      <c r="C138" s="95"/>
+      <c r="D138" s="97"/>
+      <c r="E138" s="83"/>
+      <c r="F138" s="104"/>
+      <c r="G138" s="34"/>
+      <c r="H138" s="102"/>
+      <c r="I138" s="149">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J138" s="134"/>
-      <c r="K138" s="135"/>
+      <c r="J138" s="148"/>
+      <c r="K138" s="80"/>
     </row>
     <row r="139" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A139" s="136"/>
-      <c r="B139" s="137"/>
-      <c r="C139" s="138"/>
-      <c r="D139" s="139"/>
-      <c r="E139" s="129"/>
-      <c r="F139" s="130"/>
-      <c r="G139" s="131"/>
-      <c r="H139" s="132"/>
-      <c r="I139" s="133">
+      <c r="A139" s="81"/>
+      <c r="B139" s="82"/>
+      <c r="C139" s="95"/>
+      <c r="D139" s="97"/>
+      <c r="E139" s="83"/>
+      <c r="F139" s="104"/>
+      <c r="G139" s="34"/>
+      <c r="H139" s="102"/>
+      <c r="I139" s="149">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J139" s="134"/>
-      <c r="K139" s="135"/>
+      <c r="J139" s="148"/>
+      <c r="K139" s="80"/>
     </row>
     <row r="140" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A140" s="136"/>
-      <c r="B140" s="137"/>
-      <c r="C140" s="138"/>
-      <c r="D140" s="139"/>
-      <c r="E140" s="141"/>
-      <c r="F140" s="130"/>
-      <c r="G140" s="131"/>
-      <c r="H140" s="142"/>
-      <c r="I140" s="143">
+      <c r="A140" s="81"/>
+      <c r="B140" s="82"/>
+      <c r="C140" s="95"/>
+      <c r="D140" s="97"/>
+      <c r="E140" s="83"/>
+      <c r="F140" s="104"/>
+      <c r="G140" s="34"/>
+      <c r="H140" s="103"/>
+      <c r="I140" s="147">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J140" s="134"/>
-      <c r="K140" s="135"/>
+      <c r="J140" s="148"/>
+      <c r="K140" s="80"/>
     </row>
     <row r="141" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A141" s="136"/>
-      <c r="B141" s="137"/>
-      <c r="C141" s="138"/>
-      <c r="D141" s="139"/>
-      <c r="E141" s="141"/>
-      <c r="F141" s="130"/>
-      <c r="G141" s="131"/>
-      <c r="H141" s="144"/>
-      <c r="I141" s="143">
+      <c r="A141" s="81"/>
+      <c r="B141" s="82"/>
+      <c r="C141" s="95"/>
+      <c r="D141" s="97"/>
+      <c r="E141" s="83"/>
+      <c r="F141" s="104"/>
+      <c r="G141" s="34"/>
+      <c r="H141" s="103"/>
+      <c r="I141" s="147">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J141" s="134"/>
-      <c r="K141" s="135"/>
+      <c r="J141" s="148"/>
+      <c r="K141" s="80"/>
     </row>
     <row r="142" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A142" s="136"/>
-      <c r="B142" s="137"/>
-      <c r="C142" s="138"/>
-      <c r="D142" s="139"/>
-      <c r="E142" s="141"/>
-      <c r="F142" s="130"/>
-      <c r="G142" s="131"/>
-      <c r="H142" s="144"/>
-      <c r="I142" s="143">
+      <c r="A142" s="81"/>
+      <c r="B142" s="82"/>
+      <c r="C142" s="95"/>
+      <c r="D142" s="97"/>
+      <c r="E142" s="83"/>
+      <c r="F142" s="104"/>
+      <c r="G142" s="34"/>
+      <c r="H142" s="103"/>
+      <c r="I142" s="147">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J142" s="134"/>
-      <c r="K142" s="135"/>
+      <c r="J142" s="148"/>
+      <c r="K142" s="80"/>
     </row>
     <row r="143" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A143" s="136"/>
-      <c r="B143" s="137"/>
-      <c r="C143" s="138"/>
-      <c r="D143" s="139"/>
-      <c r="E143" s="141"/>
-      <c r="F143" s="130"/>
-      <c r="G143" s="131"/>
-      <c r="H143" s="132"/>
-      <c r="I143" s="133">
+      <c r="A143" s="81"/>
+      <c r="B143" s="82"/>
+      <c r="C143" s="95"/>
+      <c r="D143" s="97"/>
+      <c r="E143" s="83"/>
+      <c r="F143" s="104"/>
+      <c r="G143" s="34"/>
+      <c r="H143" s="102"/>
+      <c r="I143" s="149">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J143" s="134"/>
-      <c r="K143" s="135"/>
+      <c r="J143" s="148"/>
+      <c r="K143" s="80"/>
     </row>
     <row r="144" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A144" s="136"/>
-      <c r="B144" s="137"/>
-      <c r="C144" s="138"/>
-      <c r="D144" s="139"/>
-      <c r="E144" s="129"/>
-      <c r="F144" s="130"/>
-      <c r="G144" s="131"/>
-      <c r="H144" s="132"/>
-      <c r="I144" s="133">
+      <c r="A144" s="81"/>
+      <c r="B144" s="82"/>
+      <c r="C144" s="95"/>
+      <c r="D144" s="97"/>
+      <c r="E144" s="83"/>
+      <c r="F144" s="104"/>
+      <c r="G144" s="34"/>
+      <c r="H144" s="102"/>
+      <c r="I144" s="149">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J144" s="134"/>
-      <c r="K144" s="135"/>
+      <c r="J144" s="148"/>
+      <c r="K144" s="80"/>
     </row>
     <row r="145" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A145" s="136"/>
-      <c r="B145" s="137"/>
-      <c r="C145" s="138"/>
-      <c r="D145" s="139"/>
-      <c r="E145" s="129"/>
-      <c r="F145" s="130"/>
-      <c r="G145" s="131"/>
-      <c r="H145" s="132"/>
-      <c r="I145" s="133">
+      <c r="A145" s="81"/>
+      <c r="B145" s="82"/>
+      <c r="C145" s="95"/>
+      <c r="D145" s="97"/>
+      <c r="E145" s="83"/>
+      <c r="F145" s="104"/>
+      <c r="G145" s="34"/>
+      <c r="H145" s="102"/>
+      <c r="I145" s="149">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J145" s="134"/>
-      <c r="K145" s="135"/>
+      <c r="J145" s="148"/>
+      <c r="K145" s="80"/>
     </row>
     <row r="146" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A146" s="136"/>
-      <c r="B146" s="137"/>
-      <c r="C146" s="138"/>
-      <c r="D146" s="139"/>
-      <c r="E146" s="129"/>
-      <c r="F146" s="130"/>
-      <c r="G146" s="131"/>
-      <c r="H146" s="132"/>
-      <c r="I146" s="133">
+      <c r="A146" s="81"/>
+      <c r="B146" s="82"/>
+      <c r="C146" s="95"/>
+      <c r="D146" s="97"/>
+      <c r="E146" s="83"/>
+      <c r="F146" s="104"/>
+      <c r="G146" s="34"/>
+      <c r="H146" s="102"/>
+      <c r="I146" s="149">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J146" s="134"/>
-      <c r="K146" s="135"/>
+      <c r="J146" s="148"/>
+      <c r="K146" s="80"/>
     </row>
     <row r="147" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A147" s="136"/>
-      <c r="B147" s="137"/>
-      <c r="C147" s="138"/>
-      <c r="D147" s="139"/>
-      <c r="E147" s="129"/>
-      <c r="F147" s="130"/>
-      <c r="G147" s="131"/>
-      <c r="H147" s="132"/>
-      <c r="I147" s="133">
+      <c r="A147" s="81"/>
+      <c r="B147" s="82"/>
+      <c r="C147" s="95"/>
+      <c r="D147" s="97"/>
+      <c r="E147" s="83"/>
+      <c r="F147" s="104"/>
+      <c r="G147" s="34"/>
+      <c r="H147" s="102"/>
+      <c r="I147" s="149">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J147" s="134"/>
-      <c r="K147" s="135"/>
+      <c r="J147" s="148"/>
+      <c r="K147" s="80"/>
     </row>
     <row r="148" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A148" s="136"/>
-      <c r="B148" s="137"/>
-      <c r="C148" s="138"/>
-      <c r="D148" s="139"/>
-      <c r="E148" s="145"/>
-      <c r="F148" s="130"/>
-      <c r="G148" s="131"/>
-      <c r="H148" s="132"/>
-      <c r="I148" s="133">
+      <c r="A148" s="81"/>
+      <c r="B148" s="82"/>
+      <c r="C148" s="95"/>
+      <c r="D148" s="97"/>
+      <c r="E148" s="98"/>
+      <c r="F148" s="104"/>
+      <c r="G148" s="34"/>
+      <c r="H148" s="102"/>
+      <c r="I148" s="149">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J148" s="134"/>
-      <c r="K148" s="135"/>
+      <c r="J148" s="148"/>
+      <c r="K148" s="80"/>
     </row>
     <row r="149" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A149" s="136"/>
-      <c r="B149" s="137"/>
-      <c r="C149" s="138"/>
-      <c r="D149" s="139"/>
-      <c r="E149" s="129"/>
-      <c r="F149" s="130"/>
-      <c r="G149" s="131"/>
-      <c r="H149" s="132"/>
-      <c r="I149" s="133">
+      <c r="A149" s="81"/>
+      <c r="B149" s="82"/>
+      <c r="C149" s="95"/>
+      <c r="D149" s="97"/>
+      <c r="E149" s="83"/>
+      <c r="F149" s="104"/>
+      <c r="G149" s="34"/>
+      <c r="H149" s="102"/>
+      <c r="I149" s="149">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J149" s="134"/>
-      <c r="K149" s="135"/>
+      <c r="J149" s="148"/>
+      <c r="K149" s="80"/>
     </row>
     <row r="150" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A150" s="146"/>
-      <c r="B150" s="147"/>
-      <c r="C150" s="148" t="s">
-        <v>18</v>
-      </c>
-      <c r="D150" s="149"/>
-      <c r="E150" s="150"/>
-      <c r="F150" s="150"/>
-      <c r="G150" s="151"/>
-      <c r="H150" s="132"/>
-      <c r="I150" s="133">
+      <c r="A150" s="101"/>
+      <c r="B150" s="84"/>
+      <c r="C150" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" s="84"/>
+      <c r="E150" s="99"/>
+      <c r="F150" s="105"/>
+      <c r="G150" s="6"/>
+      <c r="H150" s="102"/>
+      <c r="I150" s="149">
         <f>SUM(I127:J149)</f>
         <v>0</v>
       </c>
-      <c r="J150" s="134"/>
-      <c r="K150" s="152"/>
+      <c r="J150" s="148"/>
+      <c r="K150" s="85"/>
     </row>
   </sheetData>
-  <mergeCells count="168">
+  <mergeCells count="170">
     <mergeCell ref="I147:J147"/>
     <mergeCell ref="I148:J148"/>
     <mergeCell ref="I149:J149"/>
@@ -16035,6 +16069,16 @@
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="F26:I26"/>
     <mergeCell ref="J26:K26"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="F1:I1"/>
@@ -16052,26 +16096,22 @@
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B2:C2"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25 D50 D75 D100 D125 D150" xr:uid="{D91065FE-FD2D-44CD-84E9-17AECA26AEE6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25 D100 D125 D50 D75 D150" xr:uid="{D91065FE-FD2D-44CD-84E9-17AECA26AEE6}">
       <formula1>"サンゲツ,リリカラ,東リ,シンコール,ニップ,トキワ,タジマ,量産クロス,量産タイルカーペット,＃１０００,タイルカーペット,カーペット,塩ビタイル,ノンスリップシート,トミタ,"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.70866141732283472" right="0" top="0.39370078740157483" bottom="0.19685039370078741" header="0.39370078740157483" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" scale="97" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.59055118110236227" right="0" top="0.19685039370078741" bottom="0.19685039370078741" header="0.39370078740157483" footer="0.19685039370078741"/>
+  <pageSetup paperSize="9" scale="91" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="25" max="10" man="1"/>
+    <brk id="50" max="10" man="1"/>
+  </rowBreaks>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -16079,13 +16119,13 @@
           <x14:formula1>
             <xm:f>マスタ!$D$4:$D$25</xm:f>
           </x14:formula1>
-          <xm:sqref>C3:C24 C28:C49 C53:C74 C78:C99 C103:C124 C128:C149</xm:sqref>
+          <xm:sqref>C3:C24 C78:C99 C103:C124 C28:C49 C53:C74 C128:C149</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{901BE4D4-BC47-40EB-AF64-9145548203A5}">
           <x14:formula1>
             <xm:f>マスタ!$B$4:$B$30</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G25 G28:G50 G53:G75 G78:G100 G103:G125 G128:G150</xm:sqref>
+          <xm:sqref>G3:G25 G78:G100 G103:G125 G28:G50 G53:G75 G128:G150</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -16110,193 +16150,193 @@
     </row>
     <row r="3" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" s="7"/>
     </row>
     <row r="15" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
     </row>
     <row r="16" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
     </row>
     <row r="17" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -16304,7 +16344,7 @@
     </row>
     <row r="18" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
